--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0010.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0010.xlsx
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Được rồi, đồng ý. Đôi khi ta hơi... quá tay. Như tắt một thiết bị còn bật, diệt một chương trình nguy hiểm, hay Dodgem một tài liệu tham khảo đúng lúc. Đại loại thế.</t>
+          <t>Được rồi, đồng ý. Đôi khi ta hơi... quá tay. Như tắt một thiết bị còn bật, diệt một chương trình nguy hiểm, hay ném một tài liệu tham khảo đúng lúc. Đại loại thế.</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Sabercat Reaver không phải trò đùa đâu. Chúng là những sát thủ hàng đầu thật sự. Siêu nhanh luôn. Nhưng vẫn phải ăn bụi sau lưng ta!
+          <t>Kẻ Tàn Sát Mèo Đao không phải trò đùa đâu. Chúng là những sát thủ hàng đầu thật sự. Siêu nhanh luôn. Nhưng vẫn phải ăn bụi sau lưng tao!
 Lưu ý: Chỉ dành cho dân chuyên tìm ý tưởng thiết kế đường đua. TUYỆT ĐỐI KHÔNG THỬ NGHIỆM.
 Huafeng</t>
         </is>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Ta tưởng sau khi tốt nghiệp, mình có thể kiếm tiền từ vẽ tranh để trả nợ bố mẹ số tiền họ đã bỏ ra cho ta học trường mỹ thuật. Nhưng hóa ra chỉ là mơ thôi.</t>
+          <t>Tao tưởng sau khi tốt nghiệp, mình có thể kiếm tiền từ vẽ tranh để trả nợ bố mẹ số tiền họ đã bỏ ra cho tao học trường mỹ thuật. Nhưng hóa ra chỉ là mơ thôi.</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Có người yêu cầu thêm một con mèo nữa, nhưng cả đội đang bị tra hỏi ở Patrol Station vì bị nhầm là trộm mèo trong nhiệm vụ hôm qua.</t>
+          <t>Có người yêu cầu thêm một con mèo nữa, nhưng cả đội đang bị tra hỏi ở Trạm Tuần Tra vì bị nhầm là trộm mèo trong nhiệm vụ hôm qua.</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Con mèo liếc tôi rồi nói: "Ngốc. Nếu không có lũ chuột trộm dầu, chúng nó giữ ta làm gì? Tốt hơn là mỗi ngày được chút dầu, còn hơn là không có gì."</t>
+          <t>Con mèo liếc tôi rồi nói: "Ngốc. Nếu không có lũ chuột trộm dầu, chúng nó giữ tao làm gì? Tốt hơn là mỗi ngày được chút dầu, còn hơn là không có gì."</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Theo kế hoạch của hắn, chúng tôi đã mất nhiều ngày dụ một Discord vào lãnh địa của con quái thú. Mục tiêu là kích động bản năng lãnh thổ của nó và đẩy chúng vào cuộc chiến.</t>
+          <t>Theo kế hoạch của hắn, chúng tôi đã mất nhiều ngày dụ một Tacet Discord vào lãnh địa của con quái thú. Mục tiêu là kích động bản năng lãnh thổ của nó và đẩy chúng vào cuộc chiến.</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Uncle nói đúng. Dù chúng ta đã sa cơ lỡ vận, nhưng miễn Valeria – Thanh Kiếm Bất Diệt – còn được nhớ đến, gia tộc ta sẽ lại vươn lên, với danh tiếng của nàng soi đường!</t>
+          <t>Chú nói đúng. Dù chúng ta đã sa cơ lỡ vận, nhưng miễn Valeria – Thanh Kiếm Bất Diệt – còn được nhớ đến, gia tộc ta sẽ lại vươn lên, với danh tiếng của nàng soi đường!</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Hmm... đúng vậy. Các trận đấu đấu sĩ ở Septimont bắt nguồn từ nghi lễ săn bắn, cả hai đều nhằm chuẩn bị cho chúng ta chiến đấu với Bóng Tối Tràn Về. Chắc hẳn có điểm tương đồng nào đó.</t>
+          <t>Hừm... đúng vậy. Các trận đấu đấu sĩ ở Septimont bắt nguồn từ nghi lễ săn bắn, cả hai đều nhằm chuẩn bị cho chúng ta chiến đấu với Bóng Tối Tràn Về. Chắc hẳn có điểm tương đồng nào đó.</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Tôi đã muốn bắt đầu lại từ đầu, học mọi thứ như một thợ săn mới, nhưng áp lực đó chỉ khiến việc tiếp thu càng khó khăn hơn. Cảm ơn! Giờ tôi đã thoải mái hơn nhiều rồi. Đến lúc xem lại ghi chép thôi!</t>
+          <t>Tôi đã muốn bắt đầu lại từ đầu, học mọi thứ như một thợ săn mới, nhưng áp lực đó chỉ khiến việc tiếp thu càng khó khăn hơn. Cảm ơn cậu! Giờ tôi đã thoải mái hơn nhiều rồi. Đến lúc xem lại ghi chép thôi!</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Nó là một kẻ ô nhục. Bất cẩn, thô lỗ, và làm ô danh Đền Thờ. Nó thậm chí còn nói xấu cả những thành viên đáng kính của Senate. Tin tôi đi, giao du với nó chỉ khiến danh tiếng của cậu thêm tệ hại.</t>
+          <t>Nó là một kẻ ô nhục. Bất cẩn, thô lỗ, và làm ô danh Đền Thờ. Nó thậm chí còn nói xấu cả những thành viên đáng kính của Thượng Nghị Viện. Tin tôi đi, giao du với nó chỉ khiến danh tiếng của cậu thêm tệ hại.</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Người ta bảo tộc Wootters từng sống ở Thành Septimont từ rất lâu rồi. Nhưng sau đợt Hắc Triều đầu tiên, họ chuyển lên Sanguis Plateaus và định cư ở đây.</t>
+          <t>Người ta bảo tộc Wootters từng sống ở Thành Septimont từ rất lâu rồi. Nhưng sau đợt Hắc Triều đầu tiên, họ chuyển lên Cao Nguyên Sanguis và định cư ở đây.</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Khi chữa trị cho họ, hãy chú ý thật kỹ vào mắt. Nếu ai đó Dodge ánh nhìn hoặc nhìn vô hồn, rất có thể họ đang gặp phải những triệu chứng này.</t>
+          <t>Khi chữa trị cho họ, hãy chú ý thật kỹ vào mắt. Nếu ai đó né tránh ánh nhìn hoặc nhìn vô hồn, rất có thể họ đang gặp phải những triệu chứng này.</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Bạn gặp Lingyang đang trò chuyện với mấy đứa trẻ. Cậu giới thiệu bạn với Liondance Troupe và kể về vài truyền thống của Jinzhou. Cậu mời bạn cùng chuẩn bị cho buổi múa lân sắp tới—và còn rủ đi ăn vặt trên đường nữa.</t>
+          <t>Bạn gặp Lingyang đang trò chuyện với mấy đứa trẻ. Cậu giới thiệu bạn với Đoàn Múa Lân và kể về vài truyền thống của Jinzhou. Cậu mời bạn cùng chuẩn bị cho buổi múa lân sắp tới—và còn rủ đi ăn vặt trên đường nữa.</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Bei Shi kể rằng Bei Ji luôn cảm thấy tội lỗi về cô. Cô cũng thổ lộ nỗi sợ hãi đối với "Quái Thú Leng Keng", xuất phát từ một lần gặp phải nó ngoài hoang dã.</t>
+          <t>Bắc Thi kể rằng Bắc Cơ luôn cảm thấy tội lỗi về cô. Cô cũng thổ lộ nỗi sợ hãi đối với "Quái Thú Leng Keng", xuất phát từ một lần gặp phải nó ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Lingyang đến quán trà để giải quyết một yêu cầu còn dang dở. Chủ quán lo lắng về việc Lingyang luôn đặt người khác lên trên bản thân và nhờ cậu kiểm tra giúp. Cậu đồng ý hỗ trợ.</t>
+          <t>Linh Dương đến quán trà để giải quyết một yêu cầu còn dang dở. Chủ quán lo lắng về việc Linh Dương luôn đặt người khác lên trên bản thân và nhờ cậu kiểm tra giúp. Cậu đồng ý hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Lần này không cần giữ nguyên vẹn {Male=hắn;Female=nàng} đâu, chỉ cần một chút ý thức cơ bản là đủ. Fractsidus đã dạy ta cách xử lý một cơ thể như thế.</t>
+          <t>Lần này không cần giữ nguyên vẹn {Male=him;Female=her} đâu, chỉ cần một chút ý thức cơ bản là đủ. Fractsidus đã dạy ta cách xử lý một cơ thể như thế.</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Đừng lúc nào cũng căng thẳng thế. Thỉnh thoảng, cậu phải cho bản thân nghỉ ngơi chứ. Cố quá cũng chẳng tốt đâu. Hay thử tham gia một sự kiện xem sao?</t>
+          <t>Đừng lúc nào cũng căng thẳng thế. Thỉnh thoảng, mày phải cho bản thân nghỉ ngơi chứ. Cố quá cũng chẳng tốt đâu. Hay thử tham gia một sự kiện xem sao?</t>
         </is>
       </c>
     </row>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Bạn bước vào Sonoro Sphere cùng Jiyan và bắt gặp những ảo ảnh đang bàn tán về đội tạm thời từ mười năm trước. Jiyan dường như biết rõ câu chuyện nhưng lại Dodge chủ đề. Rồi trước khi bạn kịp phản ứng, những ảo ảnh ấy biến thành Tacet Discord và tấn công.</t>
+          <t>Bạn bước vào Sonoro Sphere cùng Jiyan và bắt gặp những ảo ảnh đang bàn tán về đội tạm thời từ mười năm trước. Jiyan dường như biết rõ câu chuyện nhưng lại né tránh chủ đề. Rồi trước khi bạn kịp phản ứng, những ảo ảnh ấy biến thành Tacet Discord và tấn công.</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Jiyan giải thích rằng những Tacet Discord này đang tái hiện lại Riverside Games từ một thập kỷ trước và tiết lộ anh từng là thành viên của đội lập kỷ lục hồi đó. Anh tin rằng những bất thường này có liên quan đến họ. Bạn nghe thấy tiếng chuông ở Knell Square và tiếp tục khám phá.</t>
+          <t>Jiyan giải thích rằng những Tacet Discord này đang tái hiện lại Riverside Games từ một thập kỷ trước và tiết lộ anh từng là thành viên của đội lập kỷ lục hồi đó. Anh tin rằng những bất thường này có liên quan đến họ. Bạn nghe thấy tiếng chuông ở Quảng trường Knell và tiếp tục khám phá.</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Jiyan suy đoán rằng Quả Cầu Sonoro được cấu thành từ những Dư Âm của đồng đội đã khuất, bị mắc kẹt ở đây và buộc phải sống lại ký ức của mình. Tần số của họ bị kẹt lại trong một trận chiến quá khứ với Tacet Discord và họ cầu xin sự giúp đỡ của cậu. Dưới sự dẫn dắt của tiếng chuông, cậu tiến sâu hơn vào Sonoro.</t>
+          <t>Jiyan suy đoán rằng Sonoro Sphere được cấu thành từ những Dư Âm của đồng đội đã khuất, bị mắc kẹt ở đây và buộc phải sống lại ký ức của mình. Tần số của họ bị kẹt lại trong một trận chiến quá khứ với Tacet Discord và họ cầu xin sự giúp đỡ của cậu. Dưới sự dẫn dắt của tiếng chuông, cậu tiến sâu hơn vào Sonoro.</t>
         </is>
       </c>
     </row>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Ghế sofa êm ái, lửa reo trong lò sưởi, kệ sách ngăn nắp... Thấy chưa, ta không chỉ lo chuyện cứu thế đâu. Cuộc sống riêng của ta cũng ổn định lắm.</t>
+          <t>Ghế sofa êm ái, lửa reo trong lò sưởi, kệ sách ngăn nắp... Thấy chưa, tao không chỉ lo chuyện cứu thế đâu. Cuộc sống riêng của tao cũng ổn định lắm.</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Uống rượu giữa ban ngày thế này? Bạn do dự, tự hỏi liệu có nên nhận lời khi còn nhiều việc phải làm. Dù lần này đành từ chối, nhưng biết đâu lần sau sẽ đồng ý.</t>
+          <t>Uống rượu giữa ban ngày thế này? bạn/bạn do dự, tự hỏi liệu có nên nhận lời khi còn nhiều việc phải làm. Dù lần này đành từ chối, nhưng biết đâu lần sau sẽ đồng ý.</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>À, mình nghe nói Royan Marketn vừa có hàng mới về. Đồ chơi, màu vẽ, máy chơi game, phụ kiện xe máy... Nhiều thứ mình muốn mua quá trời luôn...</t>
+          <t>À, mình nghe nói Chợ Royan vừa có hàng mới về. Đồ chơi, màu vẽ, máy chơi game, phụ kiện xe máy... Nhiều thứ mình muốn mua quá trời luôn...</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Thấy bức tượng đồ sộ đằng kia không? Đó là Fabius, người sáng lập Septimont và người đầu tiên được tôn vinh là "Hero of Heroes". Chính Fabius đã đặt tên cho vùng đất vĩ đại này – một cái tên hùng tráng, gợi nhớ về quê hương tổ tiên. Người ta kể rằng, trước khi bị buộc rời bỏ quê nhà, họ từng sống trên vùng đất bao quanh bởi bảy ngọn đồi.</t>
+          <t>Thấy bức tượng đồ sộ đằng kia không? Đó là Fabius, người sáng lập Septimont và người đầu tiên được tôn vinh là "Anh Hùng Trong Các Anh Hùng". Chính Fabius đã đặt tên cho vùng đất vĩ đại này – một cái tên hùng tráng, gợi nhớ về quê hương tổ tiên. Người ta kể rằng, trước khi bị buộc rời bỏ quê nhà, họ từng sống trên vùng đất bao quanh bởi bảy ngọn đồi.</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Sanguis Plateaus, vùng biên ải của vực thẳm... vô số anh hùng vô danh đã ngã xuống trên bãi săn này. Mong hương Asphodel mang lại bình yên cho linh hồn họ, và đôi cánh Gryphon đưa họ trở về Vale of Glory.</t>
+          <t>Cao Nguyên Sanguis, vùng biên ải của vực thẳm... vô số anh hùng vô danh đã ngã xuống trên bãi săn này. Mong hương Asphodel mang lại bình yên cho linh hồn họ, và đôi cánh Gryphon đưa họ trở về Vale of Glory.</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Khu vực kho lưu trữ này sử dụng công nghệ tiên tiến do gia tộc Montelli phát triển. Echoes được gắn cố định trên giá đỡ, giúp bảo quản mà không cần đến Terminal chuyên dụng.</t>
+          <t>Khu vực kho lưu trữ này sử dụng công nghệ tiên tiến do gia tộc Montelli phát triển. Echo được gắn cố định trên giá đỡ, giúp bảo quản mà không cần đến Terminal chuyên dụng.</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Haha, ừ thì, theo ta biết về nhà Montelli, khả năng đó xảy ra còn thấp hơn cả việc cả dân Ragunna đột nhiên mê Pizza Tropicale!</t>
+          <t>Haha, ừ thì, theo tao biết về nhà Montelli, khả năng đó xảy ra còn thấp hơn cả việc cả dân Ragunna đột nhiên mê Pizza Tropicale!</t>
         </is>
       </c>
     </row>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Đúng rồi, những Echoes ở khu vực kho lưu trữ này! Chúng đều có vẻ mặt ma quái như vậy. Chúng dùng để làm gì nhỉ? Chẳng giống tí nào với những Echoes ở Ragunna City cả.</t>
+          <t>Đúng rồi, những Echo ở khu vực kho lưu trữ này! Chúng đều có vẻ mặt ma quái như vậy. Chúng dùng để làm gì nhỉ? Chẳng giống tí nào với những Echo ở Ragunna City cả.</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Hắn hoặc là vùi đầu vào sách vở, hoặc là đi lòng vòng quanh mấy con Echoes... Tôi còn thấy hắn đưa tay chạm vào cánh của một con! Lẩm bẩm một mình suốt, nữa chứ.</t>
+          <t>Hắn hoặc là vùi đầu vào sách vở, hoặc là đi lòng vòng quanh mấy con Echo... Tôi còn thấy hắn đưa tay chạm vào cánh của một con! Lẩm bẩm một mình suốt, nữa chứ.</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Khu vực ngầm được chia thành ba khu chính: Precious Metals and Artworks Depository, Kho Lưu Trữ Echo, và Kho Tài Năng. Dù bạn muốn cất giữ tài sản quý giá hay phô diễn sự sáng tạo, Averardo Vault luôn sẵn sàng hỗ trợ tối đa với dịch vụ không đối thủ.</t>
+          <t>Khu vực ngầm được chia thành ba khu chính: Kho Tàng Kim Loại và Tác Phẩm Nghệ Thuật, Kho Lưu Trữ Tiếng Vọng, và Kho Tài Năng. Dù bạn muốn cất giữ tài sản quý giá hay phô diễn sự sáng tạo, Averardo Vault luôn sẵn sàng hỗ trợ tối đa với dịch vụ không đối thủ.</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Gulpuff được phân loại là Echo cấp thấp. Nếu muốn lưu trữ, anh phải tự mua bảo hiểm và trả phí lưu trữ dựa trên đơn vị chứa.</t>
+          <t>Gulpuff được phân loại là Tiếng Vọng cấp thấp. Nếu muốn lưu trữ, anh phải tự mua bảo hiểm và trả phí lưu trữ dựa trên đơn vị chứa.</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Ừ, được thôi, không có gì đâu cháu. Nếu cháu thực sự muốn tìm hiểu những câu chuyện, thì hãy đến Helm Village đi. Mấy lão già ở đó cũng chẳng trẻ hơn ta đâu. Chúng sẽ có những câu chuyện để kể cho cháu nghe.</t>
+          <t>Ừ, được thôi, không có gì đâu cháu. Nếu cháu thực sự muốn tìm hiểu những câu chuyện, thì hãy đến Làng Helm đi. Mấy lão già ở đó cũng chẳng trẻ hơn ta đâu. Chúng sẽ có những câu chuyện để kể cho cháu nghe.</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Nhớ Xiehua Village chứ? Ta từng gửi cảnh báo đến Trung tâm Nghiên cứu Khí hậu Wutherological của Huaxu Academy, báo trước về một Waveworn tiềm ẩn ở khu vực đó.</t>
+          <t>Nhớ Xiehua Village chứ? Ta từng gửi cảnh báo đến Trung tâm Nghiên cứu Khí hậu Wutherological của Học viện Huaxu, báo trước về một Waveworn tiềm ẩn ở khu vực đó.</t>
         </is>
       </c>
     </row>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Ngăn chặn thảm họa, gìn giữ tia lửa văn minh, và giám sát Lament—đó là sứ mệnh của chúng ta tại Black Shores, lời hứa ta đã trao cho nhân loại.</t>
+          <t>Ngăn chặn thảm họa, gìn giữ tia lửa văn minh, và giám sát Lament—đó là sứ mệnh của chúng ta tại Bờ Biển Đen, lời hứa ta đã trao cho nhân loại.</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Let's see... "Theo quan sát, sự va chạm của các Ma Trận Sao cho thấy mâu thuẫn và loại trừ lẫn nhau giữa logic của các mô hình tính toán..."</t>
+          <t>Để xem nào... "Theo quan sát, sự va chạm của các Ma Trận Sao cho thấy mâu thuẫn và loại trừ lẫn nhau giữa logic của các mô hình tính toán..."</t>
         </is>
       </c>
     </row>
@@ -20664,8 +20664,8 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận thưởng. Mua các mặt hàng có gắn thẻ &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; trong các mục &lt;color=#ad893a&gt;Đề Xuất - Bundles Hàng Tuần, Đề Xuất - Bundles Lunite, Bộ Sưu Tập - Special Offers, Trang Phục - Ngoại Hình Xe, và Mua Lunite&lt;/color&gt; tại Cửa hàng để nhận Nhẫn Ánh Trăng.
-Khi sự kiện Moonlit Path kết thúc, Nhẫn Ánh Trăng sẽ hết hạn và không được chuyển đổi thành vật phẩm khác.</t>
+          <t>Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận thưởng. Mua các mặt hàng có gắn thẻ &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; trong các mục &lt;color=#ad893a&gt;Đề Xuất - Gói Hàng Tuần, Đề Xuất - Gói Lunite, Bộ Sưu Tập - Ưu Đãi Đặc Biệt, Trang Phục - Ngoại Hình Xe, và Mua Lunite&lt;/color&gt; tại Cửa Hàng để nhận Nhẫn Ánh Trăng.
+Khi sự kiện Con Đường Ánh Trăng kết thúc, Nhẫn Ánh Trăng sẽ hết hạn và không được chuyển đổi thành vật phẩm khác.</t>
         </is>
       </c>
     </row>
@@ -20796,8 +20796,8 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Trong khoảng thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Thread Withdrawn&lt;/color&gt;, nhấn &lt;color=Highlight&gt;Dodge&lt;/color&gt; về phía trước để kích hoạt &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt;.
-Trong thời gian này, giữ &lt;color=Highlight&gt;Dodge&lt;/color&gt; để trượt một đoạn ngắn trên vũ khí.</t>
+          <t>Trong khoảng thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Thread Withdrawn&lt;/color&gt;, nhấn &lt;color=Highlight&gt;Né Tránh&lt;/color&gt; về phía trước để kích hoạt &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt;.
+Trong thời gian này, giữ &lt;color=Highlight&gt;Né Tránh&lt;/color&gt; để trượt một đoạn ngắn trên vũ khí.</t>
         </is>
       </c>
     </row>
@@ -20862,7 +20862,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Khi đánh bại một Discord, tần số còn sót lại có thể biến thành &lt;color=#ffd12f&gt;Echo&lt;/color&gt;. Bạn có thể nhận EXP &lt;color=#ffd12f&gt;Data Bank&lt;/color&gt; bằng cách hấp thụ Echo lần đầu. Nâng cấp Data Bank để tăng xác suất rơi Echo.</t>
+          <t>Khi đánh bại một Tacet Discord, tần số còn sót lại có thể biến thành &lt;color=#ffd12f&gt;Echo&lt;/color&gt;. Bạn có thể nhận EXP &lt;color=#ffd12f&gt;Ngân Hàng Dữ Liệu&lt;/color&gt; bằng cách hấp thụ Echo lần đầu. Nâng cấp Ngân Hàng Dữ Liệu để tăng xác suất rơi Echo.</t>
         </is>
       </c>
     </row>
@@ -20927,7 +20927,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Mô-đun Grapple&lt;/color&gt; giúp vượt qua địa hình phức tạp. Khi sử dụng trực tiếp, người điều khiển có thể &lt;color=#ffd12f&gt;nhảy&lt;/color&gt; lên một đoạn ngắn.</t>
+          <t>&lt;color=#ffd12f&gt;Mô-đun Móc Câu&lt;/color&gt; giúp vượt qua địa hình phức tạp. Khi sử dụng trực tiếp, người điều khiển có thể &lt;color=#ffd12f&gt;nhảy&lt;/color&gt; lên một đoạn ngắn.</t>
         </is>
       </c>
     </row>
@@ -20992,7 +20992,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Sản phẩm của một Quả Cầu Sonoro sụp đổ, vương vãi khắp nơi trên thế giới. Nó lưu giữ những ký ức không bị méo mó của quá khứ. Nếu may mắn tìm thấy một cái, &lt;color=#ffd12f&gt;các Relic Merchant&lt;/color&gt; sẽ sẵn lòng đổi lấy những món đồ giá trị.</t>
+          <t>Sản phẩm của một Sonoro Sphere sụp đổ, vương vãi khắp nơi trên thế giới. Nó lưu giữ những ký ức không bị méo mó của quá khứ. Nếu may mắn tìm thấy một cái, &lt;color=#ffd12f&gt;các Thương Nhân Di Vật&lt;/color&gt; sẽ sẵn lòng đổi lấy những món đồ giá trị.</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21124,7 @@
       <c r="M318" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;Tacetite Fulminate&lt;/color&gt; tỏa ánh sáng vàng, bên trong chứa đựng năng lượng bất ổn.
-Sau khi mở khóa Công cụ, bạn có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để lấy nó.</t>
+Sau khi mở khóa Tiện Ích, bạn có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để lấy nó.</t>
         </is>
       </c>
     </row>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Khi Inferno Rider thực hiện kỹ năng lao tới, bạn có thể dùng &lt;color=#ffd12f&gt;Echo đặc biệt&lt;/color&gt; để phòng thủ. Phòng thủ thành công sẽ khiến nó rơi vào trạng thái &lt;color=#ffd12f&gt;Bất Động&lt;/color&gt;.</t>
+          <t>Khi Kỵ Sĩ Hỏa Ngục thực hiện kỹ năng lao tới, bạn có thể dùng &lt;color=#ffd12f&gt;Echo đặc biệt&lt;/color&gt; để phòng thủ. Phòng thủ thành công sẽ khiến nó rơi vào trạng thái &lt;color=#ffd12f&gt;Bất Động&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21319,7 +21319,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Phá hủy chân, đầu và &lt;color=#ffd12f&gt;quả chuông cổ&lt;/color&gt; để làm giảm đáng kể &lt;color=#ffd12f&gt;Concerto Vibrancy&lt;/color&gt; của nó. Phản công các &lt;color=#ffd12f&gt;quả cầu băng khổng lồ&lt;/color&gt; cũng sẽ làm giảm mạnh &lt;color=#ffd12f&gt;Concerto Vibrancy&lt;/color&gt;, &lt;color=#ffd12f&gt;nhưng không hề dễ dàng chút nào&lt;/color&gt;.</t>
+          <t>Phá hủy chân, đầu và &lt;color=#ffd12f&gt;quả chuông cổ&lt;/color&gt; để làm giảm đáng kể &lt;color=#ffd12f&gt;Sức Mạnh Rung Động&lt;/color&gt; của nó. Phản công các &lt;color=#ffd12f&gt;quả cầu băng khổng lồ&lt;/color&gt; cũng sẽ làm giảm mạnh &lt;color=#ffd12f&gt;Sức Mạnh Rung Động&lt;/color&gt;, &lt;color=#ffd12f&gt;nhưng không hề dễ dàng chút nào&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào nút có biểu tượng kính lúp ở góc dưới bên trái của thẻ để xem chi tiết. Dùng Prestige Points tại đó để mở khóa.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút có biểu tượng kính lúp ở góc dưới bên trái của thẻ để xem chi tiết. Dùng Điểm Uy Tín tại đó để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Khi trở thành "Apex Duelist", cậu sẽ mở khóa Challenges Vô Tận, nơi cậu có thể thách đấu bất kỳ đấu sĩ nào ở Septimont. Cho họ thấy thế nào mới là đỉnh nhất!</t>
+          <t>Khi trở thành "Duelist Đỉnh Cao", cậu sẽ mở khóa Thử Thách Vô Tận, nơi cậu có thể thách đấu bất kỳ đấu sĩ nào ở Septimont. Cho họ thấy thế nào mới là đỉnh nhất!</t>
         </is>
       </c>
     </row>
@@ -21516,7 +21516,7 @@
       <c r="M324" t="inlineStr">
         <is>
           <t>Sau khi tương tác với Corroder gần đó, &lt;color=#ffd12f&gt;Corroder&lt;/color&gt; sẽ tạm thời &lt;color=#ffd12f&gt;theo&lt;/color&gt; cậu.
-Dẫn chúng đến gần &lt;color=#ffd12f&gt;Spikes&lt;/color&gt;, chúng sẽ hòa tan cột vàng bên cạnh, cuối cùng làm tan Spikes.</t>
+Dẫn chúng đến gần &lt;color=#ffd12f&gt;Gai Nhọn&lt;/color&gt;, chúng sẽ hòa tan cột vàng bên cạnh, cuối cùng làm tan Gai Nhọn.</t>
         </is>
       </c>
     </row>
@@ -21582,8 +21582,8 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Nơi hoang dã, nơi các cụm Tacetite phát triển tự do, đôi khi có thể thấy &lt;color=#ffd12f&gt;Spikes&lt;/color&gt; chặn đường hoặc &lt;color=#ffd12f&gt;phong ấn&lt;/color&gt; các vật phẩm hay câu đố.
-Hãy quan sát kỹ xung quanh Spikes để tìm &lt;color=#ffd12f&gt;Kẻ Ăn Mòn&lt;/color&gt;. Chúng sẽ phân hủy Spikes.</t>
+          <t>Nơi hoang dã, nơi các cụm Tacetite phát triển tự do, đôi khi có thể thấy &lt;color=#ffd12f&gt;Gai Nhọn&lt;/color&gt; chặn đường hoặc &lt;color=#ffd12f&gt;phong ấn&lt;/color&gt; các vật phẩm hay câu đố.
+Hãy quan sát kỹ xung quanh Gai Nhọn để tìm &lt;color=#ffd12f&gt;Kẻ Ăn Mòn&lt;/color&gt;. Chúng sẽ phân hủy Gai Nhọn.</t>
         </is>
       </c>
     </row>
@@ -21780,7 +21780,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Đánh bại&lt;/color&gt; các &lt;color=#ffd12f&gt;Tacet Discords&lt;/color&gt; gần đó để đảm bảo kích hoạt thành công &lt;color=#ffd12f&gt;Sound Emulator&lt;/color&gt;. Hoàn thành thử thách để nhận thưởng.</t>
+          <t>Hạ gục các &lt;color=#ffd12f&gt;Tacet Discord&lt;/color&gt; gần đó để đảm bảo kích hoạt thành công &lt;color=#ffd12f&gt;Bộ Mô Phỏng Âm Thanh&lt;/color&gt;. Hoàn thành thử thách để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -21910,7 +21910,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;Trung Tâm Tín Hiệu&lt;/color&gt; bị khóa, cậu có thể dùng &lt;color=#ffd12f&gt;Sensor&lt;/color&gt; để xác định vị trí các &lt;color=#ffd12f&gt;Bảng Điều Khiển Tín Hiệu&lt;/color&gt; kết nối với nó nhưng bị ẩn ở nơi khác.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Trung Tâm Tín Hiệu&lt;/color&gt; bị khóa, cậu có thể dùng &lt;color=#ffd12f&gt;Cảm Biến&lt;/color&gt; để xác định vị trí các &lt;color=#ffd12f&gt;Bảng Điều Khiển Tín Hiệu&lt;/color&gt; kết nối với nó nhưng bị ẩn ở nơi khác.</t>
         </is>
       </c>
     </row>
@@ -21976,7 +21976,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Khối Tạ được đặt gần Bàn Áp Lực. Sau khi mở khóa Công cụ, bạn có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để nhấc &lt;color=#ffd12f&gt;Khối Tạ&lt;/color&gt; và đặt nó vào vị trí &lt;color=#ffd12f&gt;hạ cánh&lt;/color&gt; dự định.
+          <t>Khối Tạ được đặt gần Bàn Áp Lực. Sau khi mở khóa Tiện Ích, bạn có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để nhấc &lt;color=#ffd12f&gt;Khối Tạ&lt;/color&gt; và đặt nó vào vị trí &lt;color=#ffd12f&gt;hạ cánh&lt;/color&gt; dự định.
 Khi Khối Tả được đặt lên &lt;color=#ffd12f&gt;Bàn Áp Lực&lt;/color&gt;, nó sẽ &lt;color=#ffd12f&gt;dính chặt&lt;/color&gt; vào đó.</t>
         </is>
       </c>
@@ -22111,7 +22111,7 @@
       <c r="M333" t="inlineStr">
         <is>
           <t>Khối Tạ nằm gần Bệ Áp Lực. Dùng Levitator để nhấc Khối Tạ, sau đó dùng Levitator lần nữa để đặt nó vào vị trí hạ cánh dự định.
-Unlock Công cụ để sử dụng tính năng này.</t>
+Mở khóa Tiện Ích để sử dụng tính năng này.</t>
         </is>
       </c>
     </row>
@@ -22178,7 +22178,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Sau khi mở khóa Công cụ, bạn có thể dùng &lt;color=#ffd12f&gt;Bộ Bay Lơ Lửng&lt;/color&gt;
+          <t>Sau khi mở khóa Tiện Ích, bạn có thể dùng &lt;color=#ffd12f&gt;Bộ Bay Lơ Lửng&lt;/color&gt;
 để đặt các &lt;color=#ffd12f&gt;Linh Kiện&lt;/color&gt; rải rác trở lại Ma Trận.
 Khi dùng Bộ Bay Lơ Lửng, bạn có thể &lt;color=#ffd12f&gt;xoay&lt;/color&gt; để điều chỉnh hướng của Linh Kiện.</t>
         </is>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Bộ Lặp Khóa&lt;/color&gt; phát ra Xung Giải Mã theo các hướng khác nhau. Sau khi mở khóa Công cụ, cậu có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để đặt Bộ Lặp Khóa lên Encryption Block. Trong khi sử dụng Levitator, cậu có thể &lt;color=#ffd12f&gt;xoay&lt;/color&gt; để điều chỉnh hướng phát Xung Giải Mã.</t>
+          <t>&lt;color=#ffd12f&gt;Bộ Lặp Khóa&lt;/color&gt; phát ra Xung Giải Mã theo các hướng khác nhau. Sau khi mở khóa Tiện Ích, cậu có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để đặt Bộ Lặp Khóa lên Khối Mã Hóa. Trong khi sử dụng Levitator, cậu có thể &lt;color=#ffd12f&gt;xoay&lt;/color&gt; để điều chỉnh hướng phát Xung Giải Mã.</t>
         </is>
       </c>
     </row>
@@ -22311,8 +22311,8 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#ffd12f&gt;Grapple Shooter Dây&lt;/color&gt; để bắn ra các &lt;color=#ffd12f&gt;Points Móc Tạm Thời&lt;/color&gt;, giúp Resonators di chuyển nhanh chóng.
-Unlock Công cụ để sử dụng.</t>
+          <t>Dùng &lt;color=#ffd12f&gt;Súng Móc Dây&lt;/color&gt; để bắn ra các &lt;color=#ffd12f&gt;Điểm Móc Tạm Thời&lt;/color&gt;, giúp Resonator dịch chuyển nhanh chóng.
+Mở khóa Tiện Ích để sử dụng.</t>
         </is>
       </c>
     </row>
@@ -22379,7 +22379,7 @@
       <c r="M337" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;Bình Nổ&lt;/color&gt; sẽ kích hoạt một vụ &lt;color=#ffd12f&gt;nổ dữ dội&lt;/color&gt; nếu bị tác động.
-Sau khi mở khóa Công cụ, cậu có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để nhặt Bình Nổ trên các cành cây.</t>
+Sau khi mở khóa Tiện Ích, cậu có thể dùng &lt;color=#ffd12f&gt;Levitator&lt;/color&gt; để nhặt Bình Nổ trên các cành cây.</t>
         </is>
       </c>
     </row>
@@ -22444,7 +22444,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Theo chỉ dẫn trên đường ray, &lt;color=#ffd12f&gt;tấn công Magnetic Cube&lt;/color&gt; để di chuyển nó theo hướng chỉ định. Khi các Magnetic Cube &lt;color=#ffd12f&gt;đến được&lt;/color&gt; các &lt;color=#ffd12f&gt;Băng Tải Từ Tính&lt;/color&gt; đã định, thử thách sẽ hoàn thành.</t>
+          <t>Theo chỉ dẫn trên đường ray, &lt;color=#ffd12f&gt;tấn công Khối Từ Tính&lt;/color&gt; để di chuyển nó theo hướng chỉ định. Khi các Khối Từ Tính &lt;color=#ffd12f&gt;đến được&lt;/color&gt; các &lt;color=#ffd12f&gt;Băng Tải Từ Tính&lt;/color&gt; đã định, thử thách sẽ hoàn thành.</t>
         </is>
       </c>
     </row>
@@ -22511,7 +22511,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Biến thành &lt;color=#ffd12f&gt;Cruisewing&lt;/color&gt; để tham gia thử thách bay và thu thập càng nhiều Xu càng tốt trong thời gian quy định để kiếm điểm.
+          <t>Biến hình thành &lt;color=#ffd12f&gt;Cruisewing&lt;/color&gt; để tham gia thử thách bay và thu thập càng nhiều Xu càng tốt trong thời gian quy định để kiếm điểm.
 Điểm càng cao, phần thưởng mở khóa càng giá trị.
 Trong lúc bay, &lt;color=#ffd12f&gt;xoay góc nhìn&lt;/color&gt; để đổi hướng. Giữ nút Tăng Tốc để &lt;color=#ffd12f&gt;tăng tốc&lt;/color&gt;, giữ nút Giảm Tốc để &lt;color=#ffd12f&gt;giảm tốc&lt;/color&gt;.</t>
         </is>
@@ -22647,7 +22647,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Sau khi tương tác với cơ chế con rối, cậu sẽ vào trạng thái &lt;color=#ffd12f&gt;Control Con Rối&lt;/color&gt;.
+          <t>Sau khi tương tác với cơ chế con rối, cậu sẽ vào trạng thái &lt;color=#ffd12f&gt;Điều Khiển Con Rối&lt;/color&gt;.
 Trong trạng thái này, cậu có thể để con rối ở lại &lt;color=#ffd12f&gt;bất cứ khi nào cần&lt;/color&gt; và &lt;color=#ffd12f&gt;chuyển về&lt;/color&gt; điều khiển Resonator của mình.
 Hãy tận dụng con rối để tiếp cận những nơi ngoài tầm với và vô hiệu hóa cơ chế laser chắn đường.</t>
         </is>
@@ -22910,8 +22910,8 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Những khu vực nguy hiểm hơn chứa Discord với Cấp Glory cao hơn. Có lẽ nên tăng Cấp Glory để nhận Buffs trước khi đối đầu với Discord cấp cao hơn.
-Quận Cũ có năm khu vực. Mỗi khu vực đều có một Discord đặc biệt với Cấp Glory cao nhất trong khu. Đánh bại chúng để nhận &lt;color=#ffd12f&gt;phần thưởng hậu hĩnh&lt;/color&gt;.</t>
+          <t>Những khu vực nguy hiểm hơn chứa Tacet Discord với Cấp Vinh Quang cao hơn. Có lẽ nên tăng Cấp Vinh Quang để nhận Buff trước khi đối đầu với Tacet Discord cấp cao hơn.
+Quận Cũ có năm khu vực. Mỗi khu vực đều có một Tacet Discord đặc biệt với Cấp Vinh Quang cao nhất trong khu. Đánh bại chúng để nhận &lt;color=#ffd12f&gt;phần thưởng hậu hĩnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22978,8 +22978,8 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Ngọn Cờ Chinh Phục có thể tìm thấy trong Khu Vực Trial.
-Tương tác với những ngọn cờ có ánh sáng vàng sẽ nhận được Points Săn và Points Trial.
+          <t>Ngọn Cờ Chinh Phục có thể tìm thấy trong Khu Vực Thử Thách.
+Tương tác với những ngọn cờ có ánh sáng vàng sẽ nhận được Điểm Săn và Điểm Thử Thách.
 Tương tác với những ngọn cờ có ánh sáng xanh sẽ nhận được Hiệu Ứng Tăng Cường.</t>
         </is>
       </c>
@@ -23045,7 +23045,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Những Tacet Discord trong Giấc Mộng đã bị Nhiễm Khuẩn và khó nhằn hơn nhiều so với đồng loại bình thường. Ngươi phải tìm ra điểm yếu của chúng để đánh bại. Hoàn thành Challenge Goal hoặc sử dụng Kỹ Năng Special sẽ mang lại hiệu ứng tăng cường mạnh mẽ trước Tacet Discord trong Giấc Mộng Nhiễm Khuẩn.</t>
+          <t>Những Tacet Discord trong Giấc Mộng đã bị Nhiễm Khuẩn và khó nhằn hơn nhiều so với đồng loại bình thường. Ngươi phải tìm ra điểm yếu của chúng để đánh bại. Hoàn thành Mục Tiêu Thử Thách hoặc sử dụng Kỹ Năng Đặc Biệt sẽ mang lại hiệu ứng tăng cường mạnh mẽ trước Tacet Discord trong Giấc Mộng Nhiễm Khuẩn.</t>
         </is>
       </c>
     </row>
@@ -23112,7 +23112,7 @@
       <c r="M348" t="inlineStr">
         <is>
           <t>Những sợi tần số chứa đầy oán hận đang chảy qua những sợi chỉ kỳ lạ này...
-Khi Bitter Resentment kết vỏ, hãy dùng &lt;color=#ffd12f&gt;Hero's Slash&lt;/color&gt; để tiêu diệt chúng.</t>
+Khi Oán Hận Đắng Cay kết vỏ, hãy dùng &lt;color=#ffd12f&gt;Hero's Slash&lt;/color&gt; để tiêu diệt chúng.</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23242,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Nếu Cấp Độ Glory của cậu thấp hơn mức khuyến nghị cho Banner tiếp theo, cậu có thể tăng Cấp Độ Glory bằng cách &lt;color=#ffd12f&gt;kích hoạt Banner Chinh Phục, khám phá khu vực hiện tại hoặc đánh bại TD&lt;/color&gt;.</t>
+          <t>Nếu Cấp Độ Vinh Quang của cậu thấp hơn mức khuyến nghị cho Banner tiếp theo, cậu có thể tăng Cấp Độ Vinh Quang bằng cách &lt;color=#ffd12f&gt;kích hoạt Banner Chinh Phục, khám phá khu vực hiện tại hoặc đánh bại TD&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23308,8 +23308,8 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nhấn vào Echoes trong danh sách bên trái để thêm vào bộ bài.
-Mỗi bộ bài chỉ chứa được Echoes của tối đa 2 Thuộc Tính. Để thay đổi Thuộc Tính, hãy xóa Echoes của Thuộc Tính cũ khỏi bộ bài trước.</t>
+          <t>Nhấn vào Echo trong danh sách bên trái để thêm vào bộ bài.
+Mỗi bộ bài chỉ chứa được Echo của tối đa 2 Thuộc Tính. Để thay đổi Thuộc Tính, hãy xóa Echo của Thuộc Tính cũ khỏi bộ bài trước.</t>
         </is>
       </c>
     </row>
@@ -23375,8 +23375,8 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Một bộ bài gồm 21 Echoes, trong đó phải có một Core Echoes và phần còn lại là Thường Echoes. Số lượng Echoes trong bộ bài bị giới hạn tối đa và yêu cầu tối thiểu để có thể bắt đầu trận đấu. 
-Mỗi Echoes sở hữu các Skills khác nhau. Một số Skills có thể bổ trợ hoặc tăng cường cho nhau. Hãy lưu ý điều này khi xây dựng bộ bài của bạn.</t>
+          <t>Một bộ bài gồm 21 Echo, trong đó phải có một Core Echo và phần còn lại là Normal Echo. Số lượng Echo trong bộ bài bị giới hạn tối đa và yêu cầu tối thiểu để có thể bắt đầu trận đấu. 
+Mỗi Echo sở hữu các Kỹ năng khác nhau. Một số Kỹ năng có thể bổ trợ hoặc tăng cường cho nhau. Hãy lưu ý điều này khi xây dựng bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -23442,8 +23442,8 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Kéo Echoes từ tay bạn vào Vùng Triển khai để Triển khai chúng.
-Bên trái là Hàng Tiền Tuyến, bên phải là Hàng Backline. Hãy sắp xếp Echoes một cách chiến lược dựa trên tầm tấn công của chúng.</t>
+          <t>Kéo Echo từ tay bạn vào Vùng Triển Khai để Triển Khai chúng.
+Bên trái là Hàng Tiền Tuyến, bên phải là Hàng Hậu Cần. Hãy sắp xếp Echo một cách chiến lược dựa trên tầm tấn công của chúng.</t>
         </is>
       </c>
     </row>
@@ -23509,8 +23509,8 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Kéo Echoes từ tay hoặc Vùng Triển Khai vào Khu Tái Cấu Trúc bên phải để Tái Cấu Trúc.
-Tái Cấu Trúc Echoes sẽ xáo lại nó vào bộ bài và phục hồi 1 Năng Lượng. Bạn có thể rút lại Echoes đã Tái Cấu Trúc trong các lượt sau.</t>
+          <t>Kéo Echo từ tay hoặc Vùng Triển Khai vào Khu Tái Cấu Trúc bên phải để Tái Cấu Trúc.
+Tái Cấu Trúc Echo sẽ xáo lại nó vào bộ bài và phục hồi 1 Năng Lượng. Bạn có thể rút lại Echo đã Tái Cấu Trúc trong các lượt sau.</t>
         </is>
       </c>
     </row>
@@ -23576,8 +23576,8 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Điều Tần kích hoạt hiệu ứng Điều Tần của Echoes. Hiệu ứng đầy đủ phụ thuộc vào Skills cụ thể.
-Chỉ có thể Điều Tần Echoes đang cầm trên tay. Bạn không thể Điều Tần một Echoes đã Triển Khai bằng một Echoes khác trong Vùng Triển Khai. Xếp chồng hai Echoes đều đang ở Vùng Triển Khai sẽ chỉ khiến chúng hoán đổi vị trí.</t>
+          <t>Điều Tần kích hoạt hiệu ứng Điều Tần của Echo. Hiệu ứng đầy đủ phụ thuộc vào Kỹ Năng cụ thể.
+Chỉ có thể Điều Tần Echo đang cầm trên tay. Bạn không thể Điều Tần một Echo đã Triển Khai bằng một Echo khác trong Vùng Triển Khai. Xếp chồng hai Echo đều đang ở Vùng Triển Khai sẽ chỉ khiến chúng hoán đổi vị trí.</t>
         </is>
       </c>
     </row>
@@ -23774,7 +23774,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Sau khi mở khóa Công cụ, bạn có thể dùng Bộ Nâng để kết nối các &lt;color=#ffd12f&gt;đường ống nhiên liệu&lt;/color&gt; với đoạn còn lại. Điều chỉnh hướng của &lt;color=#ffd12f&gt;đường ống nhiên liệu&lt;/color&gt; bằng cách xoay chúng với Bộ Nâng.</t>
+          <t>Sau khi mở khóa Tiện Ích, bạn có thể dùng Bộ Nâng để kết nối các &lt;color=#ffd12f&gt;đường ống nhiên liệu&lt;/color&gt; với đoạn còn lại. Điều chỉnh hướng của &lt;color=#ffd12f&gt;đường ống nhiên liệu&lt;/color&gt; bằng cách xoay chúng với Bộ Nâng.</t>
         </is>
       </c>
     </row>
@@ -23907,8 +23907,8 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Biến thành Inferno Rider và tăng tốc trên đường đua do những xa lộ nổi tạo thành.
-Trong lúc phi nước đại, bạn có thể điều khiển Inferno Rider vung kiếm &lt;color=#ffd12f&gt;phá hủy&lt;/color&gt; chướng ngại vật trên đường và &lt;color=#ffd12f&gt;Dodge&lt;/color&gt; biển báo giao thông.</t>
+          <t>Biến hình thành Kỵ Sĩ Hỏa Ngục và tăng tốc trên đường đua do những xa lộ nổi tạo thành.
+Trong lúc phi nước đại, bạn có thể điều khiển Kỵ Sĩ Hỏa Ngục vung kiếm &lt;color=#ffd12f&gt;phá hủy&lt;/color&gt; chướng ngại vật trên đường và &lt;color=#ffd12f&gt;né tránh&lt;/color&gt; biển báo giao thông.</t>
         </is>
       </c>
     </row>
@@ -24041,8 +24041,8 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Sensor II
-Trong quá trình khám phá, cậu có thể tìm thấy một số Acoustic Print ẩn chứa thông tin đặc biệt. Khi đến gần, chúng sẽ thay đổi hình dạng. Hãy dùng Sensor để phát hiện cơ chế ẩn hoặc rương vật tư.</t>
+          <t>Cảm Biến II
+Trong quá trình khám phá, cậu có thể tìm thấy một số Dấu Âm Thanh ẩn chứa thông tin đặc biệt. Khi đến gần, chúng sẽ thay đổi hình dạng. Hãy dùng Cảm Biến để phát hiện cơ chế ẩn hoặc rương vật tư.</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       <c r="M363" t="inlineStr">
         <is>
           <t>Móc Kéo
-Móc Kéo có thể hỗ trợ Resonators vượt qua địa hình. Sử dụng ở khu vực rộng để bật nhảy lên cao, hoặc tìm Points Móc trên bản đồ để di chuyển xa hơn.</t>
+Móc Kéo có thể hỗ trợ Resonator vượt qua địa hình. Sử dụng ở khu vực rộng để bật nhảy lên cao, hoặc tìm Điểm Móc trên bản đồ để di chuyển xa hơn.</t>
         </is>
       </c>
     </row>
@@ -24187,9 +24187,9 @@
 Dạo này, Fulmine - quản lý của Wutherium Film Studio - trông có vẻ lo lắng.
 Hạn nộp số báo tiếp theo đã cận kề, nhưng ông ta vẫn chưa chọn được bức ảnh nào ưng ý...
 Điều kiện tham gia
-Hoàn thành Chương II Act III "Điều Hôm Qua Khóc, Hôm Nay Hát" trong Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Thang Âm Quá Khứ".
+Hoàn thành Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát" trong Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Thang Âm Quá Khứ".
 Quy tắc sự kiện
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập đủ Dấu Vết Thời Gian để nhận Astrites cùng các phần thưởng khác.
 Trong tương lai, sẽ có thêm Dấu Vết Thời Gian ở các khu vực khác để thu thập.
 Tính năng này sẽ được mở vĩnh viễn, và "Thang Âm Quá Khứ" vẫn có thể truy cập qua Trace Scale sau khi sự kiện "Dấu Vết Thủy Triều" kết thúc.</t>
@@ -24266,10 +24266,10 @@
         <is>
           <t>[
 Về Sự Kiện]
-Lollo Logistics một lần nữa hợp tác với Pioneer Association hân hạnh mang đến cho bạn chiến dịch phong phú: Beyond the Waves! Tham gia và tải lên Nhật Ký Phiêu Lưu tại xe tải chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
+Lollo Logistics một lần nữa hợp tác với Hiệp Hội Tiên Phong hân hạnh mang đến cho bạn chiến dịch phong phú: Beyond the Waves! Tham gia và tải lên Nhật Ký Phiêu Lưu tại xe tải chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14.
-[Event Rules]
+[Quy Tắc Sự Kiện]
 Trong sự kiện, bạn có thể hoàn thành nhiệm vụ sự kiện mỗi ngày một lần để nhận được một số lượng Nhật Ký Phiêu Lưu nhất định.
 Mỗi Nhật Ký Phiêu Lưu có thể đổi lấy một Gói Phiêu Lưu. Gói Phiêu Lưu chứa các cơ chế đặc biệt, khi kích hoạt sẽ mở khóa một lượng lớn phần thưởng.
 Có 3 Kho Hàng cho Gói Phiêu Lưu. Khi bạn nhận đủ tất cả các kiện hàng trong một Kho, Kho tiếp theo sẽ được mở khóa.</t>
@@ -24352,7 +24352,7 @@
 Điều kiện tham gia
 Hoàn thành Chương II Màn IV "The Maiden, The Defier, The Death Crier" trong Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Scale of Past" để mở khóa.
 Quy tắc sự kiện
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập đủ tất cả Dấu Vết Thời Gian để nhận Astrites và các phần thưởng khác.
 Trong tương lai, sẽ có thêm nhiều Dấu Vết Thời Gian để thu thập ở các khu vực khác...
 Hệ thống này sẽ luôn mở, và Scale of Past vẫn có thể truy cập qua Trace Scale sau khi Acropolis Documentarian kết thúc.</t>
@@ -24489,7 +24489,7 @@
       <c r="M368" t="inlineStr">
         <is>
           <t>&lt;color=yellow&gt;Hướng Dẫn Ghép Nối:&lt;/color
-Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending Pending</t>
+Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ Đang chờ</t>
         </is>
       </c>
     </row>
@@ -24555,8 +24555,8 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Details giai đoạn&lt;/color&gt;: 
-Để trải nghiệm tối ưu khả năng đặc biệt của Resonators, các hiệu ứng tăng cường bổ sung sẽ được kích hoạt trong các giai đoạn thử nghiệm.</t>
+          <t>&lt;color=yellow&gt;Chi tiết giai đoạn&lt;/color&gt;: 
+Để trải nghiệm tối ưu khả năng đặc biệt của Resonator, các hiệu ứng tăng cường bổ sung sẽ được kích hoạt trong các giai đoạn thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -24622,8 +24622,8 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Details giai đoạn&lt;/color&gt;: 
-Để trải nghiệm tối ưu khả năng đặc biệt của Resonators, các hiệu ứng tăng cường bổ sung sẽ được kích hoạt trong các giai đoạn thử nghiệm.</t>
+          <t>&lt;color=yellow&gt;Chi tiết giai đoạn&lt;/color&gt;: 
+Để trải nghiệm tối ưu khả năng đặc biệt của Resonator, các hiệu ứng tăng cường bổ sung sẽ được kích hoạt trong các giai đoạn thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -24708,27 +24708,27 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>"[&lt;color=#c19f51&gt;Tower of Adversity&lt;/color&gt;]
+          <t>"[&lt;color=#c19f51&gt;Tháp Nghịch Cảnh&lt;/color&gt;]
 Một trung tâm thí nghiệm tổng hợp ngầm khổng lồ được xây dựng trước Thảm Họa Tacet. Nó chìm xuống biển do sự thay đổi địa hình trong Thảm Họa và chỉ mới nổi lên gần đây.
-Trạm nghiên cứu này có độ sâu hơn mười nghìn mét, chạm tới lớp Moho, và có xu hướng tiếp tục mở rộng xuống phía dưới. Đồng thời, dường như có một tiếng vọng định kỳ phát ra từ đáy giếng sâu, như thể nó đang thở. Vì vậy, giếng sâu này còn được mệnh danh là Cổng Địa Ngục.
+Trạm nghiên cứu này có độ sâu hơn mười nghìn mét, chạm tới lớp Moho, và có xu hướng tiếp tục mở rộng xuống phía dưới. Đồng thời, dường như có một Echo định kỳ phát ra từ đáy giếng sâu, như thể nó đang thở. Vì vậy, giếng sâu này còn được mệnh danh là Cổng Địa Ngục.
 Không còn nghi ngờ gì nữa, con người không có khả năng công nghiệp để xây dựng một cơ sở như vậy. Ở đáy giếng sâu, vô số bí ẩn đang chờ được khám phá...
-[&lt;color=#c19f51&gt;Chu kỳ Exploration&lt;/color&gt;]
-Môi trường của Tower of Adversity tự phục hồi theo chu kỳ &lt;color=#c19f51&gt;hai tuần&lt;/color&gt;, và dữ liệu cùng quái vật sẽ được cập nhật sau khi chu kỳ được thiết lập lại. Phần thưởng từ dữ liệu cũng sẽ được làm mới.
+[&lt;color=#c19f51&gt;Chu kỳ Thám Hiểm&lt;/color&gt;]
+Môi trường của Tháp Nghịch Cảnh tự phục hồi theo chu kỳ &lt;color=#c19f51&gt;hai tuần&lt;/color&gt;, và dữ liệu cùng quái vật sẽ được cập nhật sau khi chu kỳ được thiết lập lại. Phần thưởng từ dữ liệu cũng sẽ được làm mới.
 [&lt;color=#c19f51&gt;Cấu Trúc Ngầm&lt;/color&gt;]
-Tower of Adversity có &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực để khám phá, mỗi khu vực có &lt;color=#c19f51&gt;4&lt;/color&gt; tầng sâu. Chỉ khi người thám hiểm hoàn thành khám phá &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực ở cùng một độ sâu, họ mới có thể tiến vào các tầng sâu hơn.
-[&lt;color=#c19f51&gt;Lựa Chọn Lineup&lt;/color&gt;]
-Việc thám hiểm yêu cầu thành lập &lt;color=#c19f51&gt;3&lt;/color&gt; đội, mỗi đội sẽ hoàn thành khám phá &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực. Các Resonators đã chiến đấu sẽ bị khóa trong khu vực thám hiểm và không thể tham gia vào các khu vực khác cho đến khi hoàn thành khám phá &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực cùng độ khó. Người thám hiểm có thể chọn mở khóa thủ công, nhưng sau khi mở khóa, điểm thám hiểm của khu vực hiện tại sẽ bị đặt lại.
-[&lt;color=#c19f51&gt;Rules Exploration&lt;/color&gt;]
+Tháp Nghịch Cảnh có &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực để khám phá, mỗi khu vực có &lt;color=#c19f51&gt;4&lt;/color&gt; tầng sâu. Chỉ khi người thám hiểm hoàn thành khám phá &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực ở cùng một độ sâu, họ mới có thể tiến vào các tầng sâu hơn.
+[&lt;color=#c19f51&gt;Lựa Chọn Đội Hình&lt;/color&gt;]
+Việc thám hiểm yêu cầu thành lập &lt;color=#c19f51&gt;3&lt;/color&gt; đội, mỗi đội sẽ hoàn thành khám phá &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực. Các Resonator đã chiến đấu sẽ bị khóa trong khu vực thám hiểm và không thể tham gia vào các khu vực khác cho đến khi hoàn thành khám phá &lt;color=#c19f51&gt;3&lt;/color&gt; khu vực cùng độ khó. Người thám hiểm có thể chọn mở khóa thủ công, nhưng sau khi mở khóa, điểm thám hiểm của khu vực hiện tại sẽ bị đặt lại.
+[&lt;color=#c19f51&gt;Quy Tắc Thám Hiểm&lt;/color&gt;]
 Người thám hiểm cần tiến hành khám phá nhiều tầng trong mỗi khu vực, mỗi tầng có giới hạn thời gian nhất định. Nếu không hoàn thành thám hiểm trong thời gian quy định, sẽ bị coi là thất bại; nếu đánh bại tất cả quái vật trong thời hạn, sẽ được coi là vượt qua.
-[&lt;color=#c19f51&gt;Mức Độ Exploration&lt;/color&gt;]
+[&lt;color=#c19f51&gt;Mức Độ Thám Hiểm&lt;/color&gt;]
 Khi người thám hiểm khám phá tầng bề mặt, tầng trung chuyển và tầng sâu, mức độ thám hiểm sẽ được đánh giá theo thời gian thực dựa trên thành tích. Sau khi hoàn thành, một lượng điểm thám hiểm cố định sẽ được tính toán;
 Khi khám phá tầng đột biến, cần kết thúc thám hiểm càng sớm càng tốt để tránh ô nhiễm. &lt;color=#c19f51&gt;Càng hoàn thành nhanh&lt;/color&gt;, &lt;color=#c19f51&gt;càng nhận được nhiều điểm thám hiểm khi tính toán&lt;/color&gt;.
-[&lt;color=#c19f51&gt;Tàn Echo&lt;/color&gt;]
-Trong trạm nghiên cứu, mỗi nút khu vực sẽ có một Chủ Ảo Giác. Chủ Ảo Giác đã được tăng cường sức mạnh từ Tàn Echo của Thảm Họa, sở hữu sức mạnh vượt trội so với quái vật thông thường, thậm chí có những đặc tính giống như quy luật (như hiệu ứng tăng cường). Người thám hiểm cần lựa chọn đội hình cẩn thận dựa trên đặc tính này.
-[&lt;color=#c19f51&gt;Rules Phần Thưởng&lt;/color&gt;]
+[&lt;color=#c19f51&gt;Tàn Tiếng Vọng&lt;/color&gt;]
+Trong trạm nghiên cứu, mỗi nút khu vực sẽ có một Chủ Ảo Giác. Chủ Ảo Giác đã được tăng cường sức mạnh từ Tàn Tiếng Vọng của Thảm Họa, sở hữu sức mạnh vượt trội so với quái vật thông thường, thậm chí có những đặc tính giống như quy luật (như hiệu ứng tăng cường). Người thám hiểm cần lựa chọn đội hình cẩn thận dựa trên đặc tính này.
+[&lt;color=#c19f51&gt;Quy Tắc Phần Thưởng&lt;/color&gt;]
 Càng khám phá sâu, càng thu thập được nhiều thông tin, phần thưởng càng hậu hĩnh. Mỗi khi đạt đến một mức độ thám hiểm nhất định, phần thưởng sẽ được tính toán vào cuối chu kỳ; khi hoàn thành khám phá tầng bề mặt, tầng trung chuyển và tầng sâu, phần thưởng có thể được nhận trước.
 [&lt;color=#c19f51&gt;Hạn Chế Năng Lực&lt;/color&gt;]
-Trong Tower of Adversity, không thể nuôi dưỡng Resonators, sử dụng vật phẩm, thay đổi trang bị và Echo trong quá trình thám hiểm, và một số chức năng hệ thống cũng sẽ bị vô hiệu hóa."</t>
+Trong Tháp Nghịch Cảnh, không thể nuôi dưỡng Resonator, sử dụng vật phẩm, thay đổi trang bị và Echo trong quá trình thám hiểm, và một số chức năng hệ thống cũng sẽ bị vô hiệu hóa."</t>
         </is>
       </c>
     </row>
@@ -24806,10 +24806,10 @@
 Điều kiện tham gia
 Đạt Cấp Liên Minh 8.
 Quy tắc sự kiện
-1. Trong "Cubie Derby: Khởi Động", hoàn thành nhiệm vụ để nhận xúc xắc. Tung xúc xắc để di chuyển Cubie của Rover trên bản đồ và thu thập phần thưởng trên đường đi.
+1. Trong "Cubie Derby: Khởi Động", hoàn thành nhiệm vụ để nhận xúc xắc. Tung xúc xắc để di chuyển Cubie của Vận Mệnh Giả trên bản đồ và thu thập phần thưởng trên đường đi.
 2. Dừng chân tại một số ô để gặp gỡ các Cubie mới và mở khóa những Tăng Cường Cubie độc đáo.
-3. Event gồm 12 vòng với hai loại phần thưởng: Phần Mailởng Map và Phần Mailởng Round. Phần Mailởng Map sẽ được thu thập khi Cubie di chuyển, còn Phần Mailởng Round sẽ mở khóa sau khi hoàn thành mỗi vòng.
-Phần Mailởng Round chưa nhận sẽ vẫn có hiệu lực trong 30 ngày sau khi sự kiện kết thúc và sẽ được gửi qua Mail khi bạn đăng nhập trong khoảng thời gian này. Lưu ý rằng Phần Mailởng Map và Phần Mailởng Nhiệm Vụ Hằng Ngày/Hằng Tuần chưa nhận sẽ không được cấp lại.</t>
+3. Sự kiện gồm 12 vòng với hai loại phần thưởng: Phần Thưởng Bản Đồ và Phần Thưởng Vòng. Phần Thưởng Bản Đồ sẽ được thu thập khi Cubie di chuyển, còn Phần Thưởng Vòng sẽ mở khóa sau khi hoàn thành mỗi vòng.
+Phần Thưởng Vòng chưa nhận sẽ vẫn có hiệu lực trong 30 ngày sau khi sự kiện kết thúc và sẽ được gửi qua Thư khi bạn đăng nhập trong khoảng thời gian này. Lưu ý rằng Phần Thưởng Bản Đồ và Phần Thưởng Nhiệm Vụ Hằng Ngày/Hằng Tuần chưa nhận sẽ không được cấp lại.</t>
         </is>
       </c>
     </row>
@@ -24889,8 +24889,8 @@
 [Quy tắc sự kiện]
 1. Trong "Cubie Derby: Khởi Động", hoàn thành nhiệm vụ để kiếm xúc xắc. Tung xúc xắc để Cube của Rover di chuyển trên bản đồ và thu thập phần thưởng dọc đường.
 2. Đứng trên một số ô đặc biệt để gặp gỡ các Cube mới và mở khóa những Buff độc đáo cho Cube.
-3. Event gồm 12 vòng với hai loại phần thưởng: Phần Mailởng Map và Phần Mailởng Round. Phần Mailởng Map sẽ được thu thập khi di chuyển, còn Phần Mailởng Round sẽ mở khóa sau khi hoàn thành mỗi vòng.
-Rewards vòng chưa nhận sẽ vẫn có sẵn trong 30 ngày sau khi sự kiện kết thúc và sẽ được gửi qua Mail khi đăng nhập trong thời gian này. Lưu ý rằng phần thưởng bản đồ và phần thưởng nhiệm vụ hàng ngày/tuần chưa nhận sẽ không được cấp lại.</t>
+3. Sự kiện gồm 12 vòng với hai loại phần thưởng: Phần Thưởng Bản Đồ và Phần Thưởng Vòng. Phần Thưởng Bản Đồ sẽ được thu thập khi di chuyển, còn Phần Thưởng Vòng sẽ mở khóa sau khi hoàn thành mỗi vòng.
+Phần thưởng vòng chưa nhận sẽ vẫn có sẵn trong 30 ngày sau khi sự kiện kết thúc và sẽ được gửi qua Thư khi đăng nhập trong thời gian này. Lưu ý rằng phần thưởng bản đồ và phần thưởng nhiệm vụ hàng ngày/tuần chưa nhận sẽ không được cấp lại.</t>
         </is>
       </c>
     </row>
@@ -24964,11 +24964,11 @@
       <c r="M374" t="inlineStr">
         <is>
           <t>Về sự kiện
-KU-Lolo có ý tưởng mới: biến những kỷ niệm đáng nhớ nhất của bạn thành những Cube lưu niệm độc đáo trong Second Coming of Solaris!
+KU-Lolo có ý tưởng mới: biến những kỷ niệm đáng nhớ nhất của bạn thành những Khối Lập Phương lưu niệm độc đáo trong Sự Trở Lại Của Solaris!
 Điều kiện tham gia
 Hoàn thành Nhiệm Vụ Phụ "Thang Đo Quá Khứ" để mở khóa.
 Quy tắc sự kiện
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập đủ tất cả Dấu Vết Thời Gian để nhận Astrites và các phần thưởng khác.
 Trong tương lai, sẽ có thêm nhiều Dấu Vết Thời Gian để thu thập ở các khu vực khác…
 Đây là sự kiện thường trực. Sau khi sự kiện Memory Travelogue kết thúc, bạn vẫn có thể tiếp tục Nhiệm Vụ Phụ "Thang Đo Quá Khứ" thông qua vật phẩm đặc biệt Trace Scale.</t>
@@ -25045,16 +25045,16 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Rover thân mến,
+          <t>Vận Mệnh Giả thân mến,
 Mỗi năm vào ngày sinh nhật của bạn, chúng tôi đều chuẩn bị một món quà đặc biệt để ngày ấy thêm ý nghĩa. Dù điều ước của bạn là gì, chúng tôi tin rằng một ngày nào đó, nó sẽ thành hiện thực.
 Đây là Solaris-3, một nơi trở nên tốt đẹp hơn nhờ có bạn, một câu chuyện được viết nên cùng bạn. Dù hành trình của bạn dẫn đến đâu, hãy mang theo lời chúc phúc của chúng tôi. Và trong ngày đặc biệt này, chúng tôi mong bạn sẽ dừng chân lại một chút, dù chỉ trong thoáng chốc.
-[Thiết lập Date of Birth]
-1. Sau khi thiết lập ngày sinh và đạt Cấp Liên Minh 2, tính năng Quà Birthday sẽ được mở khóa.
+[Thiết lập Ngày Sinh]
+1. Sau khi thiết lập ngày sinh và đạt Cấp Liên Minh 2, tính năng Quà Sinh Nhật sẽ được mở khóa.
 2. Lưu ý, &lt;color=HighlightB&gt;ngày sinh không thể thay đổi sau khi thiết lập&lt;/color&gt;. Hãy chắc chắn nhập đúng ngày.
-[Quà Birthday]
+[Quà Sinh Nhật]
 1. Đăng nhập vào đúng ngày sinh nhật hoặc trong vòng 7 ngày sau đó để nhận món quà sinh nhật độc đáo.
 2. Nếu bạn bỏ lỡ 7 ngày nhưng đăng nhập trong vòng 30 ngày sau sinh nhật, món quà vẫn sẽ được gửi qua WavesLine. Nếu chưa mở khóa WavesLine, quà sẽ được gửi thẳng vào Túi Đồ.
-3. Nếu các tính năng như "Reprise of Tides" kích hoạt khi bạn đăng nhập vào ngày sinh nhật hoặc trong vòng 7 ngày sau đó, Quà Birthday sẽ được trì hoãn và gửi vào lần đăng nhập tiếp theo.
+3. Nếu các tính năng như "Reprise of Tides" kích hoạt khi bạn đăng nhập vào ngày sinh nhật hoặc trong vòng 7 ngày sau đó, Quà Sinh Nhật sẽ được trì hoãn và gửi vào lần đăng nhập tiếp theo.
 4. &lt;color=HighlightB&gt;Nếu sinh nhật của bạn đã qua khi thiết lập ngày sinh lần đầu, bạn vẫn có thể nhận quà sinh nhật và phúc lợi của năm hiện tại qua WavesLine.&lt;/color&gt;</t>
         </is>
       </c>
@@ -25128,7 +25128,7 @@
       <c r="M376" t="inlineStr">
         <is>
           <t>[Giới Thiệu]
-Để khuyến khích các Tiên Phong chia sẻ thêm về những chuyến thám hiểm Ragunna, Lollo Logistics đã hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn lên xe chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
+Để khuyến khích các Tiên Phong chia sẻ thêm về những chuyến thám hiểm Ragunna, Lollo Logistics đã hợp tác với Hiệp Hội Tiên Phong hân hạnh giới thiệu chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn lên xe chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Vượt Biển Mà Đi" để mở khóa.
 [Thể Lệ Sự Kiện]
@@ -25204,12 +25204,12 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Gửi những Rover đã đồng hành cùng chúng ta trên chặng đường dài, ta cảm ơn các ngươi đã có mặt ở đây.
+          <t>Gửi những Vận Mệnh Giả đã đồng hành cùng chúng ta trên chặng đường dài, ta cảm ơn các ngươi đã có mặt ở đây.
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 8.
 [Quy tắc sự kiện]
 Đăng nhập trong thời gian diễn ra sự kiện để nhận thưởng.
-Rewards sẽ KHÔNG được gửi lại qua thư trong game sau khi sự kiện kết thúc. Hãy chú ý thời gian sự kiện và nhận thưởng trước đó.</t>
+Phần thưởng sẽ KHÔNG được gửi lại qua thư trong game sau khi sự kiện kết thúc. Hãy chú ý thời gian sự kiện và nhận thưởng trước đó.</t>
         </is>
       </c>
     </row>
@@ -25289,21 +25289,21 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Xem Film
--Gặp gỡ nhiều sự kiện khác nhau trong Liên Hoan Film Solaris. Sử dụng Cuộn Film để khám phá câu chuyện và đạt được những kết thúc khác nhau!
--Somnoire đang tràn đầy sức mạnh bí ẩn. Khi bước vào, tất cả Synergy Giả sẽ bị tước bỏ Echoes, nhưng thay vào đó là Illusive Echoes, Metaphor và các hiệu ứng đặc biệt khác chờ được khám phá.
--Explore các đội hình và tổ hợp khác nhau để trải nghiệm chiến đấu đa dạng.
--Events này có hệ thống Kết Nối mới. Giờ đây, Synergy Giả có thể hình thành Kết Nối, mang lại nhiều hiệu ứng chiến đấu và Burst Đồng Điệu mạnh mẽ khi cấp độ tăng lên.
+          <t>Xem Phim
+-Gặp gỡ nhiều sự kiện khác nhau trong Liên Hoan Phim Solaris. Sử dụng Cuộn Phim để khám phá câu chuyện và đạt được những kết thúc khác nhau!
+-Somnoire đang tràn đầy sức mạnh bí ẩn. Khi bước vào, tất cả Resonator sẽ bị tước bỏ Echo, nhưng thay vào đó là Illusive Echo, Metaphor và các hiệu ứng đặc biệt khác chờ được khám phá.
+-Khám phá các đội hình và tổ hợp khác nhau để trải nghiệm chiến đấu đa dạng.
+-Sự kiện này có hệ thống Kết Nối mới. Giờ đây, Resonator có thể hình thành Kết Nối, mang lại nhiều hiệu ứng chiến đấu và Kích Hoạt Đồng Điệu mạnh mẽ khi cấp độ tăng lên.
 (Thuộc tính của Rover sẽ bị khóa ngay khi bạn bước vào Liên Hoan.)
-[Archive Giấc Mơ]
-Theo dõi các Metaphor và Events bạn đã thu thập trong phim và nhận phần thưởng tương ứng.
-[Danh Sách Track]
-Hoàn thành các nhiệm vụ tương ứng trong thời gian mở Danh Sách Track để nhận thưởng. Khi thời gian kết thúc, Danh Sách sẽ không còn truy cập được.
+[Lưu Trữ Giấc Mơ]
+Theo dõi các Metaphor và Sự Kiện bạn đã thu thập trong phim và nhận phần thưởng tương ứng.
+[Danh Sách Theo Dõi]
+Hoàn thành các nhiệm vụ tương ứng trong thời gian mở Danh Sách Theo Dõi để nhận thưởng. Khi thời gian kết thúc, Danh Sách sẽ không còn truy cập được.
 [Cửa Hàng Giấc Mơ]
-Kiếm "Tradable Dream" bằng cách xem phim và đổi lấy nhiều phần thưởng khác nhau.
-[Lý Thuyết Film]
-Nhận "Xúc Xắc Người Quan Sát" khi khám phá Liên Hoan Film Solaris. Sử dụng chúng trong [Lý Thuyết Film] để kích hoạt các hiệu ứng đặc biệt tăng sức mạnh cho Synergy Giả.
-[Ảnh Chụp Film]
+Kiếm "Giấc Mơ Có Thể Giao Dịch" bằng cách xem phim và đổi lấy nhiều phần thưởng khác nhau.
+[Lý Thuyết Phim]
+Nhận "Xúc Xắc Người Quan Sát" khi khám phá Liên Hoan Phim Solaris. Sử dụng chúng trong [Lý Thuyết Phim] để kích hoạt các hiệu ứng đặc biệt tăng sức mạnh cho Resonator.
+[Ảnh Chụp Phim]
 Mỗi câu chuyện có một hoặc nhiều kết thúc. Thu thập các kết thúc khác nhau để mở khóa phần thưởng cột mốc.</t>
         </is>
       </c>
@@ -25375,11 +25375,11 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>[Missions Mới]
-Pioneer Association phát hành một số nhiệm vụ hàng ngày. Rewards có thể nhận được từ Pioneer Association sau khi hoàn thành nhiệm vụ.
-[Tùy Chọn Missions]
-1. Missions có thể đến từ các quốc gia và thế lực khác nhau. Người nhận nhiệm vụ có thể tự điều chỉnh tùy chọn nhiệm vụ, nhưng không thể nhận nhiệm vụ từ các quốc gia và thế lực chưa từng tiếp xúc.
-2. Sau khi điều chỉnh tùy chọn nhiệm vụ thành "Random Country", bạn có thể nhận nhiệm vụ từ bất kỳ thế lực nào thuộc bất kỳ quốc gia nào.
+          <t>[Nhiệm Vụ Mới]
+Hiệp Hội Tiên Phong phát hành một số nhiệm vụ hàng ngày. Phần thưởng có thể nhận được từ Hiệp Hội Tiên Phong sau khi hoàn thành nhiệm vụ.
+[Tùy Chọn Nhiệm Vụ]
+1. Nhiệm vụ có thể đến từ các quốc gia và thế lực khác nhau. Người nhận nhiệm vụ có thể tự điều chỉnh tùy chọn nhiệm vụ, nhưng không thể nhận nhiệm vụ từ các quốc gia và thế lực chưa từng tiếp xúc.
+2. Sau khi điều chỉnh tùy chọn nhiệm vụ thành "Quốc gia ngẫu nhiên", bạn có thể nhận nhiệm vụ từ bất kỳ thế lực nào thuộc bất kỳ quốc gia nào.
 3. Sau khi điều chỉnh tùy chọn nhiệm vụ thành "Thế lực ngẫu nhiên", bạn có thể nhận nhiệm vụ từ bất kỳ thế lực nào thuộc quốc gia đã chọn.
 4. Việc thay đổi tùy chọn nhiệm vụ sẽ có hiệu lực vào ngày hôm sau.</t>
         </is>
@@ -25447,8 +25447,8 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Trial Resonators bao gồm Resonators Nổi Bật và Trial Resonators Permanent. Resonators Nổi Bật sẽ thay đổi định kỳ.
-Bạn có thể chiêu mộ bất kỳ Trial Resonators nào trong thử thách (dựa trên danh sách Resonators khả dụng tại thời điểm bắt đầu thử thách).</t>
+          <t>Resonator Thử Nghiệm bao gồm Resonator Nổi Bật và Resonator Thử Nghiệm Vĩnh Viễn. Resonator Nổi Bật sẽ thay đổi định kỳ.
+Bạn có thể chiêu mộ bất kỳ Resonator Thử Nghiệm nào trong thử thách (dựa trên danh sách Resonator khả dụng tại thời điểm bắt đầu thử thách).</t>
         </is>
       </c>
     </row>
@@ -25526,9 +25526,9 @@
 Mây trời chứng kiến tiếng hò reo trận mạc, đất hoang ghi dấu bước chân của những chiến binh, dòng nước cuồn cuộn mang theo ngọn lửa nhiệt huyết của kẻ dũng cảm. Nơi đây, mỗi ngóc ngách đều chứa đựng những di vật rực rỡ của một lịch sử hào hùng. Những thành phố cao chót vót, những ngọn tháp sừng sững và những bức tường kiên cố do người dân Septimont dựng nên chính là minh chứng bất diệt cho sức mạnh và ý chí của họ.
 Tại bến cảng, cậu gặp một người cha và con gái đang cãi vã. Cuộc gặp gỡ bất ngờ này đưa cậu vào hành trình khám phá lịch sử phong phú của Septimont...
 Điều kiện tham gia
-Hoàn thành Chương II Act V "Shadow Glory" trong Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Vảy Quá Khứ".
+Hoàn thành Chương II Hồi V "Bóng Tối Vinh Quang" trong Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Vảy Quá Khứ".
 Thể lệ sự kiện
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập đủ Dấu Vết Thời Gian để nhận Astrites và các phần thưởng khác.
 Trong tương lai, sẽ có thêm nhiều Dấu Vết Thời Gian ở các khu vực khác...
 Hệ thống này sẽ tồn tại vĩnh viễn, và "Vảy Quá Khứ" vẫn có thể truy cập qua Thang Dấu Vết sau khi sự kiện "Khám Phá Anh Hùng Quá Khứ" kết thúc.</t>
@@ -25607,16 +25607,16 @@
       <c r="M382" t="inlineStr">
         <is>
           <t>Về Sự Kiện
-Lollo Campaign đang đối mặt với một cuộc khủng hoảng bất ngờ! Để cứu vãn sự nghiệp của Maji và duy trì những dịch vụ tiện lợi đó, hãy giúp cậu ấy kiểm chứng độ tin cậy của Lollo Campaign nhé!
+Chiến dịch Lollo đang đối mặt với một cuộc khủng hoảng bất ngờ! Để cứu vãn sự nghiệp của Maji và duy trì những dịch vụ tiện lợi đó, hãy giúp cậu ấy kiểm chứng độ tin cậy của Chiến dịch Lollo nhé!
 Hoàn thành các chiến dịch để nhận Lollo Stamps—món quà tri ân từ Lollo Logistics. Lollo Stamps có thể đổi lấy các gói giao hàng đặc biệt từ Lollo Helper.
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 14.
-Event Rules
-Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành các Lollo Campaign để nhận được một số lượng Lollo Stamps nhất định.
+Quy Tắc Sự Kiện
+Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành các Chiến dịch Lollo để nhận được một số lượng Lollo Stamps nhất định.
 Mỗi Lollo Stamp có thể đổi lấy một gói giao hàng đặc biệt từ Lollo Helper.
 Có 3 Kho Hàng cho các gói giao hàng đặc biệt của Lollo Helper. Khi bạn thu thập đủ tất cả các gói trong một Kho Hàng, Kho Hàng tiếp theo sẽ được mở khóa.
 Nếu bạn giành được dịch vụ giao hàng đặc biệt Lollo Express, bạn có thể nhận tất cả các gói trong Kho Hàng hiện tại.
-Sau khi sự kiện kết thúc, các Lollo Campaign chưa hoàn thành sẽ không còn khả dụng, và tất cả Lollo Stamps còn lại sẽ bị thu hồi.</t>
+Sau khi sự kiện kết thúc, các Chiến dịch Lollo chưa hoàn thành sẽ không còn khả dụng, và tất cả Lollo Stamps còn lại sẽ bị thu hồi.</t>
         </is>
       </c>
     </row>
@@ -25685,11 +25685,11 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>[&lt;color=#c19f51&gt;Nhiệm Vụ Activity&lt;/color&gt;]
-Hoàn thành Nhiệm Vụ Activity để nhận thưởng. Nhiệm Vụ Activity sẽ được làm mới vào 4:00 hàng ngày.
-[&lt;color=#c19f51&gt;Phần Thưởng Activity&lt;/color&gt;]
-Thu thập Activity Points để đổi lấy phần thưởng tương ứng.
-Activity Points và Stage Rewards sẽ được làm mới vào 4:00 hàng ngày. Rewards chưa nhận sẽ bị xóa. Hãy lưu ý thời gian làm mới và nhận thưởng kịp thời.</t>
+          <t>[&lt;color=#c19f51&gt;Nhiệm Vụ Hoạt Động&lt;/color&gt;]
+Hoàn thành Nhiệm Vụ Hoạt Động để nhận thưởng. Nhiệm Vụ Hoạt Động sẽ được làm mới vào 4:00 hàng ngày.
+[&lt;color=#c19f51&gt;Phần Thưởng Hoạt Động&lt;/color&gt;]
+Thu thập Điểm Hoạt Động để đổi lấy phần thưởng tương ứng.
+Điểm Hoạt Động và Phần Thưởng Giai Đoạn sẽ được làm mới vào 4:00 hàng ngày. Phần thưởng chưa nhận sẽ bị xóa. Hãy lưu ý thời gian làm mới và nhận thưởng kịp thời.</t>
         </is>
       </c>
     </row>
@@ -25766,16 +25766,16 @@
         <is>
           <t>[
 Tổng Quan Sự Kiện]
-Một thông điệp kỳ lạ thu hút sự chú ý của bạn đến trò chơi đấu Echoes bí ẩn mang tên "Đỉnh Glory". Người ta đồn rằng vô số kẻ thách đấu đã lên đường để giành lấy danh hiệu huyền thoại "Đấu Sĩ Tối Thượng".
-"Vô số Echoes. Chiến thuật vô biên. Người tiếp theo có thể là ngươi!"
+Một thông điệp kỳ lạ thu hút sự chú ý của bạn đến trò chơi đấu Echo bí ẩn mang tên "Đỉnh Vinh Quang". Người ta đồn rằng vô số kẻ thách đấu đã lên đường để giành lấy danh hiệu huyền thoại "Đấu Sĩ Tối Thượng".
+"Vô số Echo. Chiến thuật vô biên. Người tiếp theo có thể là ngươi!"
 [Điều Kiện Tham Gia]
-Đạt Cấp Liên Minh 14 và đến Capitoline Hill trong Nhiệm Vụ Chính "Shadow Glory".
-[Event Rules]
-- Ngươi có thể triệu hồi những Echoes đặc biệt từ "Đỉnh Glory" để xây dựng bộ bài riêng và tham gia những trận đấu kịch tính khắp Septimont. Giành lấy vinh dự và danh tiếng trong khi vươn lên trở thành Đấu Sĩ Tối Thượng đầu tiên của Septimont!
-- Trong sự kiện, ngươi cần đánh bại năm Lãnh Chúa Glory và một Kẻ Chinh Phục Glory để hoàn thành thử thách và nhận phần thưởng. Sau khi giành được danh hiệu Legendary Duelist, ngươi sẽ mở khóa Endless Challenge và đối đầu với những đấu sĩ bí ẩn.
-- Event này không thể hoàn thành ở Chế Độ Hợp Tác. Hãy thoát Chế Độ Hợp Tác để tiến hành nhiệm vụ sự kiện.
-- Trong thời gian Nhận Thưởng Limited, ngươi có thể nhận những phần thưởng hậu hĩnh bằng cách hoàn thành nhiệm vụ hoặc tiêu Tinh Hoa Rạng Rỡ kiếm được từ các trận đấu trong cửa hàng Lựa Chọn Rạng Rỡ. Rewards độc quyền bao gồm Diện Mạo Echoes "Khoảnh Khắc Triumph" và nhiều hơn nữa!
-- Khi thời gian Nhận Thưởng Limited kết thúc, ngươi sẽ không thể nhận những phần thưởng này nữa, nhưng vẫn có thể tiếp tục tham gia sự kiện để kiếm Phần Thưởng Tiêu Chuẩn.</t>
+Đạt Cấp Liên Minh 14 và đến Đồi Capitoline trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang".
+[Quy Tắc Sự Kiện]
+- Ngươi có thể triệu hồi những Echo đặc biệt từ "Đỉnh Vinh Quang" để xây dựng bộ bài riêng và tham gia những trận đấu kịch tính khắp Septimont. Giành lấy vinh dự và danh tiếng trong khi vươn lên trở thành Đấu Sĩ Tối Thượng đầu tiên của Septimont!
+- Trong sự kiện, ngươi cần đánh bại năm Lãnh Chúa Vinh Quang và một Kẻ Chinh Phục Vinh Quang để hoàn thành thử thách và nhận phần thưởng. Sau khi giành được danh hiệu Đấu Sĩ Huyền Thoại, ngươi sẽ mở khóa Thử Thách Vô Tận và đối đầu với những đấu sĩ bí ẩn.
+- Sự kiện này không thể hoàn thành ở Chế Độ Hợp Tác. Hãy thoát Chế Độ Hợp Tác để tiến hành nhiệm vụ sự kiện.
+- Trong thời gian Nhận Thưởng Giới Hạn, ngươi có thể nhận những phần thưởng hậu hĩnh bằng cách hoàn thành nhiệm vụ hoặc tiêu Tinh Hoa Rạng Rỡ kiếm được từ các trận đấu trong cửa hàng Lựa Chọn Rạng Rỡ. Phần thưởng độc quyền bao gồm Diện Mạo Echo "Khoảnh Khắc Chiến Thắng" và nhiều hơn nữa!
+- Khi thời gian Nhận Thưởng Giới Hạn kết thúc, ngươi sẽ không thể nhận những phần thưởng này nữa, nhưng vẫn có thể tiếp tục tham gia sự kiện để kiếm Phần Thưởng Tiêu Chuẩn.</t>
         </is>
       </c>
     </row>
@@ -25910,10 +25910,10 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>1. Hoàn thành sự kiện sẽ mở khóa nhiều bộ Tactics tương ứng với Resonators khác nhau. Những Tactics này mang lại hiệu ứng mạnh mẽ trong các trận đấu.
-2. Mỗi Resonators có một Tactics Chủ Động và một Tactics Passive.
-Tactics Chủ Động cần Năng Lượng để sử dụng, trong khi Tactics Passive sẽ tự kích hoạt khi điều kiện được đáp ứng.
-3. Bạn cũng sẽ nhận được phần thưởng khi mở khóa bộ Tactics của mỗi Resonators lần đầu tiên.</t>
+          <t>1. Hoàn thành sự kiện sẽ mở khóa nhiều bộ Chiến Thuật tương ứng với các Resonator khác nhau. Những Chiến Thuật này mang lại hiệu ứng mạnh mẽ trong các trận đấu.
+2. Mỗi Resonator có một Chiến Thuật Chủ Động và một Chiến Thuật Bị Động.
+Chiến Thuật Chủ Động cần Năng Lượng để sử dụng, trong khi Chiến Thuật Bị Động sẽ tự kích hoạt khi điều kiện được đáp ứng.
+3. Bạn cũng sẽ nhận được phần thưởng khi mở khóa bộ Chiến Thuật của mỗi Resonator lần đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -25984,11 +25984,11 @@
       <c r="M387" t="inlineStr">
         <is>
           <t>[Huy Chương Uy Danh]
-- Nhận Huy Chương Uy Danh bằng cách đánh bại Lords of Glory hoặc tăng Cấp Độ Đấu Sĩ. Thu thập Medals Uy Danh để nhận nhiều phần thưởng khác nhau.
+- Nhận Huy Chương Uy Danh bằng cách đánh bại Lords of Glory hoặc tăng Cấp Độ Đấu Sĩ. Thu thập Huy Chương Uy Danh để nhận nhiều phần thưởng khác nhau.
 - Huy Chương Uy Danh cung cấp hiệu ứng bộ. Thu thập đủ số lượng Huy Chương cùng loại sẽ kích hoạt các hiệu ứng đặc biệt.
-[Echoes Collectiones]
-- Thu thập các Echoes khác nhau để mở khóa phần thưởng. Bạn có thể xem thông tin chi tiết về từng Echoes và sử dụng Glory Points để mở khóa những Echoes chưa sở hữu.
-- Trong sự kiện, bạn cũng có thể nâng cấp ngoại hình của Echoes.</t>
+[Bộ Sưu Tập Echo]
+- Thu thập các Echo khác nhau để mở khóa phần thưởng. Bạn có thể xem thông tin chi tiết về từng Echo và sử dụng Glory Points để mở khóa những Echo chưa sở hữu.
+- Trong sự kiện, bạn cũng có thể nâng cấp ngoại hình của Echo.</t>
         </is>
       </c>
     </row>
@@ -26063,15 +26063,15 @@
       <c r="M388" t="inlineStr">
         <is>
           <t>[Giới thiệu]
-Xưởng Dệt dưới vực sâu đã bắt đầu bất ổn, sự xáo trộn này lặng lẽ lọt vào tầm quan sát của giới quý tộc và Hội Thánh. Để ngăn chặn sự gián đoạn cuộc sống của người dân Ragunna và tránh gây hoang mang không cần thiết, cả hai bên đã tổ chức một cuộc họp kín hiếm có. Trong động thái chưa từng có, họ đã đạt được đồng thuận: cần tiến hành khảo sát lại toàn bộ cơ sở này để làm cơ sở cho các cuộc thảo luận chung về số phận của Xưởng Dệt và những Echo Chung mà nó lưu giữ.
+Xưởng Dệt dưới vực sâu đã bắt đầu bất ổn, sự xáo trộn này lặng lẽ lọt vào tầm quan sát của giới quý tộc và Hội Thánh. Để ngăn chặn sự gián đoạn cuộc sống của người dân Ragunna và tránh gây hoang mang không cần thiết, cả hai bên đã tổ chức một cuộc họp kín hiếm có. Trong động thái chưa từng có, họ đã đạt được đồng thuận: cần tiến hành khảo sát lại toàn bộ cơ sở này để làm cơ sở cho các cuộc thảo luận chung về số phận của Xưởng Dệt và những Tiếng Vọng Chung mà nó lưu giữ.
 Là người duy nhất trở về từ nơi ấy mà không hề hấn gì, cậu chính là lựa chọn tốt nhất để dẫn dắt cuộc thám hiểm này.
 [Điều kiện tham gia]
-Hoàn thành Chương II Act VII "Kẻ Bắt Giấc Mơ trong Vườn Bí Mật" của Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Vảy Quá Khứ".
+Hoàn thành Chương II Hồi VII "Kẻ Bắt Giấc Mơ trong Vườn Bí Mật" của Nhiệm Vụ Chính và Nhiệm Vụ Phụ "Vảy Quá Khứ".
 [Quy tắc sự kiện]
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập tất cả Dấu Vết Thời Gian để nhận Astrites và các phần thưởng khác.
 Trong tương lai, sẽ có thêm Dấu Vết Thời Gian để thu thập ở các khu vực khác.
-Tính năng này sẽ được mở vĩnh viễn, và "Vảy Quá Khứ" vẫn có thể truy cập thông qua Thang Dấu Vết sau khi Survey Vực Sâu kết thúc.</t>
+Tính năng này sẽ được mở vĩnh viễn, và "Vảy Quá Khứ" vẫn có thể truy cập thông qua Thang Dấu Vết sau khi Khảo sát Vực Sâu kết thúc.</t>
         </is>
       </c>
     </row>
@@ -26146,10 +26146,10 @@
           <t>Về sự kiện
 Trên vùng đất đỏ thẫm của Cao nguyên Sanguis, tiền tuyến nóng bỏng của Septimont trong cuộc chiến chống lại Dark Tide, biết bao thế hệ Võ sĩ đã khắc tên mình vào lịch sử bằng chính máu xương mình. Giờ đây, đã đến lúc ngươi bước đi trên con đường của họ, chiến đấu bên cạnh linh hồn của những anh hùng, và rèn nên một cái tên bất tử trong ngọn lửa vinh quang.
 Điều kiện tham gia
-Hoàn thành cuộc săn đầu tiên trong Nhiệm vụ Main "By Sun's Burning Hand".
+Hoàn thành cuộc săn đầu tiên trong Nhiệm vụ Chính "By Sun's Burning Hand".
 Quy tắc sự kiện
-- Event được chia thành bốn giai đoạn, mỗi giai đoạn sẽ mở khóa khi ngươi tiến triển trong Nhiệm vụ Main. Hoàn thành các nhiệm vụ sự kiện để nhận những phần thưởng hậu hĩnh.
-- Nếu có phần thưởng chưa nhận khi sự kiện kết thúc, ngươi có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.
+- Sự kiện được chia thành bốn giai đoạn, mỗi giai đoạn sẽ mở khóa khi ngươi tiến triển trong Nhiệm vụ Chính. Hoàn thành các nhiệm vụ sự kiện để nhận những phần thưởng hậu hĩnh.
+- Nếu có phần thưởng chưa nhận khi sự kiện kết thúc, ngươi có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.
 - Lưu ý rằng một số nội dung của sự kiện sẽ không khả dụng khi chơi ở chế độ Hợp tác, và Theo dõi Nhiệm vụ sẽ không hoạt động ở một số khu vực nhất định trong nhiệm vụ.</t>
         </is>
       </c>
@@ -26219,11 +26219,11 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>1. Ở Chế Độ Bẫy Chết, bạn có thể chọn một Tactics sau khi sống sót qua mỗi đợt tấn công.
-2. Một số đợt thậm chí còn thưởng nhiều Tactics hơn.
-3. Cuối một số đợt, Shop KU-Money sẽ mở, cho phép bạn mua Tactics bằng Sim Creditss.
-4. Tactics có bốn cấp độ hiếm: Xanh Lá, Xanh Dương, Purple và Vàng, với cấp độ càng cao thì hiệu ứng càng mạnh.
-5. Chúng cũng được phân loại theo Tactic Set dựa trên loại. Bạn bắt đầu với quyền truy cập vào Tactics Xanh Lá và Xanh Dương từ mỗi bộ. Khi thu thập đủ Tactics trong một bộ, các Tactics Purple và Vàng của bộ đó sẽ mở khóa.</t>
+          <t>1. Ở Chế Độ Bẫy Chết, bạn có thể chọn một Chiến Thuật sau khi sống sót qua mỗi đợt tấn công.
+2. Một số đợt thậm chí còn thưởng nhiều Chiến Thuật hơn.
+3. Cuối một số đợt, Cửa Hàng KU-Money sẽ mở, cho phép bạn mua Chiến Thuật bằng Sim Credits.
+4. Chiến Thuật có bốn cấp độ hiếm: Xanh Lá, Xanh Dương, Tím và Vàng, với cấp độ càng cao thì hiệu ứng càng mạnh.
+5. Chúng cũng được phân loại theo Bộ Chiến Thuật dựa trên loại. Bạn bắt đầu với quyền truy cập vào Chiến Thuật Xanh Lá và Xanh Dương từ mỗi bộ. Khi thu thập đủ Chiến Thuật trong một bộ, các Chiến Thuật Tím và Vàng của bộ đó sẽ mở khóa.</t>
         </is>
       </c>
     </row>
@@ -26300,17 +26300,17 @@
       <c r="M391" t="inlineStr">
         <is>
           <t>Về sự kiện
-Các đặc vụ của Black Shores từ lâu đã luôn là lực lượng tiên phong trong những thời khắc khủng hoảng. Để giảm thiểu rủi ro khi chiến đấu với Echo, Black Shores đã phát triển các thiết bị chiến đấu chuyên dụng nhằm đối phó mối đe dọa này. Valentina hiện đang dẫn dắt các cuộc thử nghiệm mô phỏng thiết bị và rất cần sự hỗ trợ của cậu để đẩy nhanh tiến độ.
+Các đặc vụ của Black Shores từ lâu đã luôn là lực lượng tiên phong trong những thời khắc khủng hoảng. Để giảm thiểu rủi ro khi chiến đấu với Tổ Tacet, Black Shores đã phát triển các thiết bị chiến đấu chuyên dụng nhằm đối phó mối đe dọa này. Valentina hiện đang dẫn dắt các cuộc thử nghiệm mô phỏng thiết bị và rất cần sự hỗ trợ của cậu để đẩy nhanh tiến độ.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue trong Nhiệm vụ Main để mở khóa.
+Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue trong Nhiệm vụ Chính để mở khóa.
 Quy tắc sự kiện
-1. Trong sự kiện này, cậu sẽ triển khai các Chiến Dịch Cơ Giới để bảo vệ Energy Matrix khỏi các đợt bùng phát Echo mô phỏng.
-2. Discords mô phỏng sẽ tấn công theo từng đợt. Cậu sẽ có thời gian để bố trí chiến lược các loại Chiến Dịch Cơ Giới trước khi mỗi đợt tấn công bắt đầu.
-3. Hãy xây dựng đội hình một cách khôn ngoan để đối phó với các loại Discord khác nhau.
-4. Tiến qua các giai đoạn để mở khóa "Chế Độ Bẫy Chết", nơi các Tactics mới mang lại sức mạnh chiến đấu vượt trội.
-5. Trong thời gian Nhận Mailởng Limited, hoàn thành nhiệm vụ để kiếm "Phiếu TD Slayer". Thu thập đủ để mở khóa Phantom: Fallacy of Không Return.
-6. Các phần thưởng chưa nhận sẽ được tự động gửi đến cậu qua Mail trong lần đăng nhập tiếp theo trong vòng 30 ngày sau khi thời gian Nhận Mailởng Limited kết thúc.
-7. Rewards giới hạn thời gian sẽ không thể nhận được sau khi thời hạn kết thúc, nhưng cậu vẫn có thể tiếp tục chơi để kiếm phần thưởng thường trực.</t>
+1. Trong sự kiện này, cậu sẽ triển khai các Chiến Dịch Cơ Giới để bảo vệ Ma Trận Năng Lượng khỏi các đợt bùng phát Tổ Tacet mô phỏng.
+2. Các Tacet Discord mô phỏng sẽ tấn công theo từng đợt. Cậu sẽ có thời gian để bố trí chiến lược các loại Chiến Dịch Cơ Giới trước khi mỗi đợt tấn công bắt đầu.
+3. Hãy xây dựng đội hình một cách khôn ngoan để đối phó với các loại Tacet Discord khác nhau.
+4. Tiến qua các giai đoạn để mở khóa "Chế Độ Bẫy Chết", nơi các Chiến Thuật mới mang lại sức mạnh chiến đấu vượt trội.
+5. Trong thời gian Nhận Thưởng Giới Hạn, hoàn thành nhiệm vụ để kiếm "Phiếu TD Slayer". Thu thập đủ để mở khóa Phantom: Fallacy of No Return.
+6. Các phần thưởng chưa nhận sẽ được tự động gửi đến cậu qua Thư trong lần đăng nhập tiếp theo trong vòng 30 ngày sau khi thời gian Nhận Thưởng Giới Hạn kết thúc.
+7. Phần thưởng giới hạn thời gian sẽ không thể nhận được sau khi thời hạn kết thúc, nhưng cậu vẫn có thể tiếp tục chơi để kiếm phần thưởng thường trực.</t>
         </is>
       </c>
     </row>
@@ -26381,8 +26381,8 @@
         <is>
           <t>Các giai đoạn trong sự kiện này hỗ trợ lưu tiến độ khi bạn thoát giữa chừng. Khi vào lại, bạn có thể chọn tiếp tục từ điểm lưu cuối hoặc bắt đầu lại từ đầu.
 Lưu ý:
-1. Progress đã lưu bao gồm: tiến trình đợt tấn công, Combat Machines đã triển khai, và các Giao Thức Vượt Trội cùng nâng cấp Combat Machines đã mở khóa khi bắt đầu giai đoạn. Trong Chế Độ Bẫy Chết, tiến độ còn bao gồm các Tactics hoặc vật phẩm đã nhận.
-2. Progress tự động lưu sau khi mỗi đợt tấn công kết thúc và sau khi chọn Tactics trong Chế Độ Bẫy Chết.
+1. Tiến độ đã lưu bao gồm: tiến trình đợt tấn công, Máy Chiến Đấu đã triển khai, và các Giao Thức Vượt Trội cùng nâng cấp Máy Chiến Đấu đã mở khóa khi bắt đầu giai đoạn. Trong Chế Độ Bẫy Chết, tiến độ còn bao gồm các Chiến Thuật hoặc vật phẩm đã nhận.
+2. Tiến độ tự động lưu sau khi mỗi đợt tấn công kết thúc và sau khi chọn Chiến Thuật trong Chế Độ Bẫy Chết.
 3. Tất cả tiến độ lưu khi thoát giữa chừng sẽ bị xóa sau khi trò chơi cập nhật phiên bản mới. Hãy lưu ý thời gian cập nhật phiên bản.</t>
         </is>
       </c>
@@ -26454,11 +26454,11 @@
       <c r="M393" t="inlineStr">
         <is>
           <t>Về nhiệm vụ
-Huaxu Academy vừa đạt được bước đột phá trong công nghệ Công cụ. Nhà nghiên cứu Lanyan cần sự trợ giúp của cậu để thử nghiệm một công cụ mới gần Học viện.
+Học viện Huaxu vừa đạt được bước đột phá trong công nghệ Utility. Nhà nghiên cứu Lanyan cần sự trợ giúp của cậu để thử nghiệm một công cụ mới gần Học viện.
 Quy tắc sự kiện
-1. Assist Lanyan thử nghiệm Công cụ Flight để nhận Astrites, vật liệu nâng cấp và các phần thưởng khác.
-2. Những Rover chưa mở khóa Flight có thể nhận khả năng này khi tham gia sự kiện. Những ai đã mở khóa Flight có thể sử dụng ngay tại Jinzhou.
-3. Event sẽ tiếp tục mở đến khi hoàn thành và tự động đóng sau một thời gian.</t>
+1. Hỗ trợ Lanyan thử nghiệm Utility Bay để nhận Astrites, vật liệu nâng cấp và các phần thưởng khác.
+2. Những Vận Mệnh Giả chưa mở khóa Bay có thể nhận khả năng này khi tham gia sự kiện. Những ai đã mở khóa Bay có thể sử dụng ngay tại Jinzhou.
+3. Sự kiện sẽ tiếp tục mở đến khi hoàn thành và tự động đóng sau một thời gian.</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
           <t>Giới Thiệu
 Dựa trên nguyên lý công nghệ sóng âm cổ xưa, máy dò này xác định vị trí các vật phẩm đặc biệt bằng cách quét tần số riêng của chúng trong khu vực.
 Hướng Dẫn
-1. Để sử dụng Máy Dò Rương, cần có Mạch Sóng Âm. Mạch Sóng Âm có thể tổng hợp tại Máy Tổng Hợp, và công thức tổng hợp Mạch Sóng Âm sẽ được mở khóa khi tăng Cấp Độ Pioneer Association.
+1. Để sử dụng Máy Dò Rương, cần có Mạch Sóng Âm. Mạch Sóng Âm có thể tổng hợp tại Máy Tổng Hợp, và công thức tổng hợp Mạch Sóng Âm sẽ được mở khóa khi tăng Cấp Độ Hiệp Hội Tiên Phong.
 2. Khi xác định được vật phẩm đặc biệt, Máy Dò Rương sẽ duy trì hoạt động. Nó sẽ tắt khi tất cả vật phẩm đã được thu thập. Bạn có thể xác định tối đa 5 vật phẩm cùng lúc.
 3. Máy Dò Rương chỉ có thể sử dụng ở những khu vực đã có Giấy Phép Sử Dụng. Không thể xác định vật phẩm đặc biệt ở những vùng không được phép.</t>
         </is>
@@ -26602,10 +26602,10 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Introduction
+          <t>Giới thiệu
 Máy Định Vị Kho Báu xác định các tần số cụ thể để nhanh chóng phát hiện những Rương Cung Ứng chưa được khám phá gần đó. Đây là công cụ không thể thiếu giúp việc thám hiểm nơi hoang dã trở nên dễ dàng hơn.
 Hướng dẫn
-1. Place một Máy Định Vị Kho Báu để quét các Rương Cung Ứng chưa được phát hiện trong phạm vi của nó.
+1. Đặt một Máy Định Vị Kho Báu để quét các Rương Cung Ứng chưa được phát hiện trong phạm vi của nó.
 2. Bạn chỉ có thể đặt tối đa 3 Máy Định Vị Kho Báu cùng lúc. Nếu vượt quá giới hạn, chiếc đầu tiên sẽ tự động thu hồi. Bạn cũng có thể thu hồi thủ công bất kỳ Máy Định Vị Kho Báu nào đã đặt.</t>
         </is>
       </c>
@@ -26684,9 +26684,9 @@
 Dưới bầu trời xanh thẳm, giữa những tòa nhà cao chót vót và phố phường tấp nập, bông tuyết nhẹ nhàng bay lượn, trong khi những dải cờ cá chép đủ màu sắc lơ lửng theo gió. Người qua kẻ lại trên phố chợ, không hay biết rằng họ chỉ là những tiếng vọng thoáng qua—những ảo ảnh phù du trong giấc mơ đang tan biến.
 Một người lạ bước vào quán cà phê và nhờ cậu giúp lấy lại những ký ức ẩn giấu trong Irideglow...
 [Điều kiện tham gia]
-Hoàn thành Nhiệm Vụ Chính Chương II - Đoạn Nối "Starlight Lấp Lánh Trong Mống Mắt" của Chronorift Metropolis và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa.
+Hoàn thành Nhiệm Vụ Chính Chương II - Đoạn Nối "Ánh Sao Lấp Lánh Trong Mống Mắt" của Chronorift Metropolis và Nhiệm Vụ Phụ "Vảy Quá Khứ" để mở khóa.
 [Quy tắc sự kiện]
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập đủ Dấu Vết Thời Gian để nhận Astrites và các phần thưởng khác.
 Trong tương lai, sẽ có thêm nhiều Dấu Vết Thời Gian để thu thập ở các khu vực khác.
 Tính năng này sẽ tồn tại vĩnh viễn, và "Vảy Quá Khứ" vẫn có thể truy cập qua Trace Scale sau khi "Những Lời Thì Thầm Của Sóng" kết thúc.</t>
@@ -26764,7 +26764,7 @@
           <t>Về sự kiện
 Shui đang tích cực tìm kiếm thành viên mới cho Câu lạc bộ Overdash danh tiếng. Nếu bạn quan tâm, hãy trò chuyện thân thiện với cậu ấy để biết thêm chi tiết nhé.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm vụ Main: Chương 1 Act 2.
+Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm vụ Chính: Chương 1 Hồi 2.
 Quy tắc sự kiện
 1. Trong sự kiện, bạn cần vượt qua một số Đường đua Chiến thuật Hologram: Overdash. Bạn có thể dịch chuyển nhanh đến bất kỳ đường đua nào để bắt đầu thử thách.
 2. Sau khi bắt đầu thử thách, hãy về đích trong thời gian quy định và cố gắng thu thập càng nhiều Hologram Token càng tốt. Khi về đích, điểm thử thách sẽ được tính dựa trên số Hologram Token thu thập được. Đạt điểm càng cao, phần thưởng càng hấp dẫn!
@@ -26836,10 +26836,10 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>[Collections Echo]
-Unlock Echo mới và nâng cao chất lượng của những Echo hiện có để tăng tiến độ Collections Echo và nhận EXP Data Bank.
-[Sonata Effect]
-Echo có thể có các thuộc tính khác nhau do sự khác biệt về dữ liệu. Tất cả các kết quả ngẫu nhiên có thể xảy ra đã được liệt kê trong Thư Viện Echo. Nhấn để xem chi tiết hiệu ứng trong Collections Sonata.</t>
+          <t>[Bộ Sưu Tập Tiếng Vọng]
+Mở khóa Tiếng Vọng mới và nâng cao chất lượng của những Tiếng Vọng hiện có để tăng tiến độ Bộ Sưu Tập Tiếng Vọng và nhận EXP Kho Dữ Liệu.
+[Hiệu Ứng Sonata]
+Tiếng Vọng có thể có các thuộc tính khác nhau do sự khác biệt về dữ liệu. Tất cả các kết quả ngẫu nhiên có thể xảy ra đã được liệt kê trong Thư Viện Tiếng Vọng. Nhấn để xem chi tiết hiệu ứng trong Bộ Sưu Tập Sonata.</t>
         </is>
       </c>
     </row>
@@ -26915,7 +26915,7 @@
       <c r="M399" t="inlineStr">
         <is>
           <t>Về sự kiện
-Mỗi Resonator đều có sở thích riêng về thức uống. Hãy trò chuyện để tìm hiểu nguyên liệu và hương vị ưa thích của họ, rồi pha chế món đồ uống hoàn hảo nhất.
+Mỗi Cộng Hưởng Giả đều có sở thích riêng về thức uống. Hãy trò chuyện để tìm hiểu nguyên liệu và hương vị ưa thích của họ, rồi pha chế món đồ uống hoàn hảo nhất.
 Hướng dẫn
 Pha chế một ly đồ uống gồm bốn bước:
 1. Chọn nguyên liệu cơ bản đầu tiên.
@@ -26923,7 +26923,7 @@
 3. Chọn thành phần bổ sung.
 4. Chọn lớp trang trí.
 Hương vị của đồ uống phụ thuộc vào sự kết hợp giữa các nguyên liệu cơ bản và thành phần bổ sung, đồng thời quyết định loại đồ uống.
-Resonator sẽ đánh giá món đồ uống dựa trên độ phù hợp với yêu cầu và sở thích cá nhân. Để nhận phần thưởng hoàn thành lần đầu, bạn cần đạt mức đánh giá "Satisfied" trở lên.
+Cộng Hưởng Giả sẽ đánh giá món đồ uống dựa trên độ phù hợp với yêu cầu và sở thích cá nhân. Để nhận phần thưởng hoàn thành lần đầu, bạn cần đạt mức đánh giá "Hài lòng" trở lên.
 Đạt mức "Rất hài lòng" để mở khóa đoạn hội thoại đặc biệt.</t>
         </is>
       </c>
@@ -26996,7 +26996,7 @@
         <is>
           <t>Về sự kiện
 Trong Trang Trí Tiệc Tùng, bạn có thể thu thập nhiều loại vật trang trí và sử dụng chúng để bài trí không gian theo ý thích.
-Area
+Khu vực
 Địa điểm tổ chức tiệc được chia thành nhiều khu vực. Mỗi khu vực có thể được trang trí tự do và độc lập.
 Thanh Vibe
 Mỗi vật trang trí cung cấp một số điểm Vibe nhất định. Tăng Thanh Vibe sẽ nâng cấp Vibe Level của khu vực, từ đó mở khóa đồ nội thất mới và phần thưởng khi đạt yêu cầu cụ thể.</t>
@@ -27065,8 +27065,8 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Hoàn thành các hoạt động sự kiện và nhiệm vụ thời hạn để kiếm Lollo Voucher cùng phần thưởng khác.
-Thu thập Lollo Voucher để đạt các mốc thưởng và nhận phần quà tương ứng.</t>
+          <t>Hoàn thành các hoạt động sự kiện và nhiệm vụ thời hạn để kiếm Phiếu Lollo cùng phần thưởng khác.
+Thu thập Phiếu Lollo để đạt các mốc thưởng và nhận phần quà tương ứng.</t>
         </is>
       </c>
     </row>
@@ -27219,10 +27219,10 @@
 [Điều kiện mở khóa]
 Hoàn thành Nhiệm Vụ Chính "When the Night Knocks" để mở khóa.
 [Quy tắc sự kiện]
-Chỉ một số Resonators nhất định có thể tham gia thử thách Depths of Illusive Realm.
-Illusive Realm chứa đựng sức mạnh đặc biệt vô hiệu hóa chỉ số Echoes của Resonators. Tuy nhiên, những Illusive Echoes, Metaphor, Token và cải tiến đặc biệt cho Resonators đang chờ đón những ai dám khám phá.
+Chỉ một số Resonator nhất định có thể tham gia thử thách Depths of Illusive Realm.
+Illusive Realm chứa đựng sức mạnh đặc biệt vô hiệu hóa chỉ số Echo của Resonator. Tuy nhiên, những Illusive Echo, Metaphor, Token và cải tiến đặc biệt cho Resonator đang chờ đón những ai dám khám phá.
 Thử nghiệm đội hình và cách xây dựng nhân vật để trải nghiệm chiến đấu khác nhau.
-Explore Illusive Realm để nhận những phần thưởng hấp dẫn.
+Khám phá Illusive Realm để nhận những phần thưởng hấp dẫn.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Memory Zone sau khi đánh bại khối mộng tưởng ở tầng sâu nhất của Illusive Realm. Sử dụng Lượt Nhận Thưởng để thu thập phần thưởng.
 Lượt Nhận Thưởng Tinh Thể Tàn Dư sẽ được đặt lại vào thứ Hai hàng tuần lúc 04:00 sáng theo giờ máy chủ.
@@ -27294,8 +27294,8 @@
       <c r="M404" t="inlineStr">
         <is>
           <t>[
-Awakening Journey]
-1. Sau khi sự kiện bắt đầu, bạn có thể nhận những phần thưởng hấp dẫn bằng cách đạt đến Cấp Liên Minh quy định.
+Hành Trình Thức Tỉnh]
+1. Sau khi sự kiện bắt đầu, bạn có thể nhận những phần thưởng hấp dẫn bằng cách đạt đến Cấp Độ Liên Minh quy định.
 2. Sự kiện này là sự kiện thường trực. Sau khi nhận hết phần thưởng, sự kiện sẽ tự động kết thúc.</t>
         </is>
       </c>
@@ -27448,21 +27448,21 @@
         <is>
           <t>Về sự kiện
 Khi những khúc ca lại vang lên, hãy để những bản nhạc dẫn lối cho bạn trên hành trình khám phá lại thế giới này.
-Có hai cấp độ phần thưởng [7-Ngày Login], với yêu cầu khác nhau về thời gian bạn đã vắng mặt.
+Có hai cấp độ phần thưởng [Đăng nhập 7 ngày], với yêu cầu khác nhau về thời gian bạn đã vắng mặt.
 Hành trình Khúc Tái Phối
 Trong Hành trình Khúc Tái Phối, bạn có thể nhận phần thưởng Quà Tặng Khúc Tái Phối bằng cách hoàn thành các nhiệm vụ nhất định.
-Bạn cũng có thể mua Unlock Nhiệm Vụ Khúc Tái Phối để nhận thêm phần thưởng.
-7-Ngày Login
-Trong sự kiện, bạn có thể nhận phần thưởng hàng ngày thông qua sự kiện 7-Ngày Login.
-Resonators Hỗ Trợ
-Trong sự kiện Reprise of Tides, bạn có thể mở khóa Resonators Hỗ Trợ để đồng hành cùng mình nếu đáp ứng yêu cầu Giai Đoạn SOL-3 của họ.
-(Lưu ý: Resonators Hỗ Trợ chỉ có thể tham gia cùng bạn ở thế giới mở và một số Sonoro Sphere định kỳ)
+Bạn cũng có thể mua Mở Khóa Nhiệm Vụ Khúc Tái Phối để nhận thêm phần thưởng.
+Đăng nhập 7 ngày
+Trong sự kiện, bạn có thể nhận phần thưởng hàng ngày thông qua sự kiện Đăng nhập 7 ngày.
+Resonator Hỗ Trợ
+Trong sự kiện Reprise of Tides, bạn có thể mở khóa Resonator Hỗ Trợ để đồng hành cùng mình nếu đáp ứng yêu cầu Giai Đoạn SOL-3 của họ.
+(Lưu ý: Resonator Hỗ Trợ chỉ có thể tham gia cùng bạn ở thế giới mở và một số Sonoro Sphere định kỳ)
 Hỗ trợ Lên Cấp
-Trong sự kiện, để giúp người chơi mới lên cấp nhanh hơn, bạn sẽ được tiếp cận các khu vực chứa vật liệu nâng cấp và Echoes được khuyến nghị cho Resonators hiện có sẵn để Triệu Hoán.
+Trong sự kiện, để giúp người chơi mới lên cấp nhanh hơn, bạn sẽ được tiếp cận các khu vực chứa vật liệu nâng cấp và Echo được khuyến nghị cho Resonator hiện có sẵn để Triệu Hoán.
 Tăng gấp đôi phần thưởng
-Trong sự kiện Reprise of Tides, hãy tận hưởng đặc quyền tăng gấp đôi phần thưởng trong cả Challenges Boss và Weekly Challenges.
+Trong sự kiện Reprise of Tides, hãy tận hưởng đặc quyền tăng gấp đôi phần thưởng trong cả Thử Thách Trùm và Thử Thách Hàng Tuần.
 Giới thiệu nội dung mới
-Truy cập trang này để xem Featured Events, Nhiệm Vụ Chính mới nhất và Resonators hiện có sẵn để Triệu Hoán.</t>
+Truy cập trang này để xem Các Sự Kiện Nổi Bật, Nhiệm Vụ Chính mới nhất và Resonator hiện có sẵn để Triệu Hoán.</t>
         </is>
       </c>
     </row>
@@ -27528,8 +27528,8 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Details giai đoạn&lt;/color&gt;: 
-Để trải nghiệm tối ưu khả năng đặc biệt của Resonators, các hiệu ứng tăng cường bổ sung sẽ được kích hoạt trong các giai đoạn thử nghiệm.</t>
+          <t>&lt;color=yellow&gt;Chi tiết giai đoạn&lt;/color&gt;: 
+Để trải nghiệm tối ưu khả năng đặc biệt của Resonator, các hiệu ứng tăng cường bổ sung sẽ được kích hoạt trong các giai đoạn thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -27595,8 +27595,8 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>1. Một số Resonators có những Companion Stories đặc biệt, giúp bạn tìm hiểu những chi tiết riêng tư nhất về họ.
-2. Companion Stories sẽ được mở khóa khi đáp ứng một số yêu cầu nhất định. Hoàn thành chúng, bạn sẽ nhận được phần thưởng hậu hĩnh.</t>
+          <t>1. Một số Resonator có những Câu Chuyện Đồng Hành đặc biệt, giúp bạn tìm hiểu những chi tiết riêng tư nhất về họ.
+2. Câu Chuyện Đồng Hành sẽ được mở khóa khi đáp ứng một số yêu cầu nhất định. Hoàn thành chúng, bạn sẽ nhận được phần thưởng hậu hĩnh.</t>
         </is>
       </c>
     </row>
@@ -27678,22 +27678,22 @@
       <c r="M409" t="inlineStr">
         <is>
           <t>Hợp Nhất Tiêu Chuẩn
-Bạn có thể Hợp Nhất hoặc Hợp Nhất Hàng Loạt 5 Echoes chưa nâng cấp thành 1 Echoes mới ngẫu nhiên trong Terminal.
-Không thể chọn Echoes đã trang bị và bị khóa làm Nguyên liệu Hợp Nhất.
-Hợp Nhất Chỉ Định
-Tính năng này mở khóa khi Data Bank đạt Cấp 15.
-Bạn có thể Hợp Nhất 5 Echoes 5-Sao chưa nâng cấp thành 1 Echoes mới ngẫu nhiên thuộc Sonata Effect mà bạn chọn.
-Không thể chọn Echoes đã trang bị và bị khóa làm Nguyên liệu Hợp Nhất.
-*Nếu Sonata Effect đã chọn hiện chỉ mở khóa Echoes Cost-1 hoặc Cost-3, Hợp Nhất Chỉ Định vẫn có thể tạo ra Echoes thuộc Cost bị khóa. Trong trường hợp này, Echoes tạo ra sẽ có Rarity 3-Sao và mở khóa mục tương ứng trong Echoes Collectiones. Sau đó, bạn có thể nhận được Echoes thuộc Cost mới mở khóa. Rarity cao nhất của Echoes nhận được sẽ phụ thuộc vào cấp độ Data Bank hiện tại.
-Echoes New
-Rarity của Echoes tạo ra phụ thuộc vào cấp độ Data Bank của bạn và không liên quan đến Rarity của Echoes được Hợp Nhất. Nâng cấp Data Bank để nhận được Echoes có Rarity cao hơn từ Data Merge.
-Data Merge chỉ tạo ra Echoes đã mở khóa.
-Sản Lượng Bổ Sung
-Hợp Nhất Tiêu Chuẩn đôi khi tạo ra Echoes bổ sung ngoài sản lượng cơ bản.
-Hợp Nhất Echoes có Rarity và Cost cao hơn sẽ tăng cơ hội nhận được Echoes bổ sung.
-*Hợp Nhất Chỉ Định không tạo ra Echoes bổ sung.
+Bạn có thể Hợp Nhất hoặc Hợp Nhất Hàng Loạt 5 Echo chưa nâng cấp thành 1 Echo mới ngẫu nhiên trong Thiết bị đầu cuối.
+Không thể chọn Echo đã trang bị và bị khóa làm Nguyên liệu Hợp Nhất.
+Hợp Nhất Có Mục Tiêu
+Tính năng này mở khóa khi Kho Dữ Liệu đạt Cấp 15.
+Bạn có thể Hợp Nhất 5 Echo 5-Sao chưa nâng cấp thành 1 Echo mới ngẫu nhiên thuộc Hiệu Ứng Sonata mà bạn chọn.
+Không thể chọn Echo đã trang bị và bị khóa làm Nguyên liệu Hợp Nhất.
+*Nếu Hiệu Ứng Sonata đã chọn hiện chỉ mở khóa Echo Cost-1 hoặc Cost-3, Hợp Nhất Có Mục Tiêu vẫn có thể tạo ra Echo thuộc Cost bị khóa. Trong trường hợp này, Echo tạo ra sẽ có Độ Hiếm 3-Sao và mở khóa mục tương ứng trong Bộ Sưu Tập Echo. Sau đó, bạn có thể nhận được Echo thuộc Cost mới mở khóa. Độ Hiếm cao nhất của Echo nhận được sẽ phụ thuộc vào cấp độ Kho Dữ Liệu hiện tại.
+Echo Mới
+Độ Hiếm của Echo tạo ra phụ thuộc vào cấp độ Kho Dữ Liệu của bạn và không liên quan đến Độ Hiếm của Echo được Hợp Nhất. Nâng cấp Kho Dữ Liệu để nhận được Echo có Độ Hiếm cao hơn từ Hợp Nhất Dữ Liệu.
+Hợp Nhất Dữ Liệu chỉ tạo ra Echo đã mở khóa.
+Sản Lượng Thêm
+Hợp Nhất Tiêu Chuẩn đôi khi tạo ra Echo bổ sung ngoài sản lượng cơ bản.
+Hợp Nhất Echo có Độ Hiếm và Cost cao hơn sẽ tăng cơ hội nhận được Echo bổ sung.
+*Hợp Nhất Có Mục Tiêu không tạo ra Echo bổ sung.
 Tự Động Chọn
-Tự Động Chọn giúp bạn nhanh chóng chọn Echoes khả dụng theo thứ tự hiển thị. Bạn có thể thay đổi cài đặt sắp xếp và lọc để thay đổi Echoes nào được hiển thị và chọn trước.</t>
+Tự Động Chọn giúp bạn nhanh chóng chọn Echo khả dụng theo thứ tự hiển thị. Bạn có thể thay đổi cài đặt sắp xếp và lọc để thay đổi Echo nào được hiển thị và chọn trước.</t>
         </is>
       </c>
     </row>
@@ -27764,11 +27764,11 @@
       <c r="M410" t="inlineStr">
         <is>
           <t>[Quy Định Sự Kiện]
-Pioneer Association đã chọn Central Plains làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Central Plains.
-Hoàn thành Survey Tasks và tích lũy Points Khảo Sát để nhận những phần thưởng giá trị từ Pioneer Association.
+Hiệp Hội Tiên Phong đã chọn Central Plains làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Central Plains.
+Hoàn thành Nhiệm Vụ Khảo Sát và tích lũy Điểm Khảo Sát để nhận những phần thưởng giá trị từ Hiệp Hội Tiên Phong.
 [Đặt Lại Nhiệm Vụ]
-Survey Tasks sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Points Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
-Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nhiệm Vụ Khảo Sát sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Điểm Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
+Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -27844,13 +27844,13 @@
       <c r="M411" t="inlineStr">
         <is>
           <t>[Giới thiệu]
-Uncle Fu bảo rằng chú có một món đồ thần kỳ.
+Chú Fu bảo rằng chú có một món đồ thần kỳ.
 Nghe nói món đồ này có hình dáng như một chiếc vảy và mang sức mạnh kỳ diệu gọi là Dấu Vết Thời Gian, có thể đưa người ta quay về những khoảnh khắc trong quá khứ...
 [Điều kiện tham gia]
 Hoàn thành nhiệm vụ phụ tiền đề Vảy Quá Khứ.
 Nhiệm vụ phụ Vảy Quá Khứ sẽ mở khóa sau khi hoàn thành nhiệm vụ chính Jinzhou Rising: Thaw of Eons.
 [Quy tắc sự kiện]
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập đủ tất cả Dấu Vết Thời Gian để nhận Astrites và các phần thưởng khác.
 Trong tương lai, sẽ có thêm nhiều Dấu Vết Thời Gian để thu thập ở các khu vực khác...
 Hệ thống này sẽ luôn mở, và các Dấu Vết trên Núi Firmament vẫn có thể truy cập qua Vảy Dấu Vết sau khi sự kiện kết thúc.</t>
@@ -27925,10 +27925,10 @@
       <c r="M412" t="inlineStr">
         <is>
           <t>[Giới thiệu]
-Uncle Fu bảo rằng chú có một món đồ thần kỳ.
+Chú Fu bảo rằng chú có một món đồ thần kỳ.
 Nghe nói món đồ này có hình dáng như một chiếc vảy và mang sức mạnh kỳ diệu gọi là Dấu Vết Thời Gian, có thể đưa người ta quay về những khoảnh khắc trong quá khứ...
 [Quy tắc sự kiện]
-Explore các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
+Khám phá các khu vực theo manh mối để thu thập những Dấu Vết Thời Gian rải rác.
 Thu thập đủ tất cả Dấu Vết Thời Gian để nhận Astrites và các phần thưởng khác.
 Trong tương lai, sẽ có thêm nhiều Dấu Vết Thời Gian để thu thập ở các khu vực khác...</t>
         </is>
@@ -28002,10 +28002,10 @@
       <c r="M413" t="inlineStr">
         <is>
           <t>["Giới Thiệu"]
-&lt;i&gt;Second Coming of Solaris&lt;/i&gt;, tác phẩm do Karl thuộc Liên bang New chấp bút, đã trở nên phổ biến rộng rãi và tiếp tục bán chạy trên toàn cầu. Cuốn sách không chỉ giàu trí tưởng tượng mà còn cung cấp những hiểu biết quý giá về địa lý và lịch sử, mang đến một thế giới quan chặt chẽ.
-Hiệp hội Tiên Phong gần đây đã giành được quyền chuyển thể game cho &lt;i&gt;Second Coming of Solaris&lt;/i&gt;, nhưng dường như họ đang gặp khó khăn và cần sự trợ giúp của cậu.
+&lt;i&gt;Sự Trở Lại Của Solaris&lt;/i&gt;, tác phẩm do Karl thuộc Liên bang Mới chấp bút, đã trở nên phổ biến rộng rãi và tiếp tục bán chạy trên toàn cầu. Cuốn sách không chỉ giàu trí tưởng tượng mà còn cung cấp những hiểu biết quý giá về địa lý và lịch sử, mang đến một thế giới quan chặt chẽ.
+Hiệp hội Tiên Phong gần đây đã giành được quyền chuyển thể game cho &lt;i&gt;Sự Trở Lại Của Solaris&lt;/i&gt;, nhưng dường như họ đang gặp khó khăn và cần sự trợ giúp của cậu.
 [Điều kiện tham gia]
-Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm vụ Main: Chương 1 Act 2.
+Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm vụ Chính: Chương 1 Hồi 2.
 [Quy tắc sự kiện]
 Mỗi ngày Maqi sẽ giao nhiệm vụ. Giao nộp vật phẩm theo yêu cầu để nhận phần thưởng.</t>
         </is>
@@ -28078,9 +28078,9 @@
       <c r="M414" t="inlineStr">
         <is>
           <t>[
-Event Rules]
-Trong sự kiện, ngươi có thể sử dụng đội hình cố định bao gồm Resonators thử nghiệm để thách đấu các giai đoạn cụ thể nhiều lần. Các Resonators thử nghiệm được cố định tại các giai đoạn nhất định và trang bị sẵn vũ khí cùng Echoes đã chọn. Trong các giai đoạn thử nghiệm, không thể thay đổi đội hình cũng như bộ vũ khí và Echoes.
-[Event Rewards]
+Quy Tắc Sự Kiện]
+Trong sự kiện, ngươi có thể sử dụng đội hình cố định bao gồm các Resonator thử nghiệm để thách đấu các giai đoạn cụ thể nhiều lần. Các Resonator thử nghiệm được cố định tại các giai đoạn nhất định và trang bị sẵn vũ khí cùng Echo đã chọn. Trong các giai đoạn thử nghiệm, không thể thay đổi đội hình cũng như bộ vũ khí và Echo.
+[Phần Thưởng Sự Kiện]
 Sau khi hoàn thành các giai đoạn sự kiện, ngươi có thể nhận phần thưởng giai đoạn trên trang sự kiện.
 Mỗi phần thưởng giai đoạn chỉ có thể nhận một lần duy nhất.
 Sau khi sự kiện kết thúc, phần thưởng cho các giai đoạn đã hoàn thành sẽ được gửi qua thư.</t>
@@ -28215,7 +28215,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Xung Giải Mã kích hoạt các Encryption Block khi đi qua chúng. Khi &lt;color=#ffd12f&gt;tất cả Encryption Block&lt;/color&gt; được &lt;color=#ffd12f&gt;kích hoạt&lt;/color&gt; đồng thời, quá trình giải mã hoàn tất.</t>
+          <t>Xung Giải Mã kích hoạt các Khối Mã Hóa khi đi qua chúng. Khi &lt;color=#ffd12f&gt;tất cả Khối Mã Hóa&lt;/color&gt; được &lt;color=#ffd12f&gt;kích hoạt&lt;/color&gt; đồng thời, quá trình giải mã hoàn tất.</t>
         </is>
       </c>
     </row>
@@ -28281,8 +28281,8 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Rewards bị khóa trong &lt;color=#ffd12f&gt;Vine Trap&lt;/color&gt;, không thể phá hủy bằng các đòn tấn công hoặc kỹ năng thông thường.
-Resonator sẽ bị &lt;color=#ffd12f&gt;hất văng&lt;/color&gt; khi &lt;color=#ffd12f&gt;tiếp cận&lt;/color&gt; trực tiếp Vine Trap.</t>
+          <t>Phần thưởng bị khóa trong &lt;color=#ffd12f&gt;Bẫy Dây Leo&lt;/color&gt;, không thể phá hủy bằng các đòn tấn công hoặc kỹ năng thông thường.
+Resonator sẽ bị &lt;color=#ffd12f&gt;hất văng&lt;/color&gt; khi &lt;color=#ffd12f&gt;tiếp cận&lt;/color&gt; trực tiếp Bẫy Dây Leo.</t>
         </is>
       </c>
     </row>
@@ -28353,13 +28353,13 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>["Details Sự Kiện"]
+          <t>["Chi Tiết Sự Kiện"]
 Shilang đang tiến hành nghiên cứu tối ưu hóa tính chất hợp kim.
-Gần đây, một Quả Cầu Sonoro đặc biệt đã xuất hiện, và Shilang phát hiện ra rằng những hợp kim ông rèn có khả năng vượt trội trong lĩnh vực này.
+Gần đây, một Sonoro Sphere đặc biệt đã xuất hiện, và Shilang phát hiện ra rằng những hợp kim ông rèn có khả năng vượt trội trong lĩnh vực này.
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14.
-[Event Rules]
-Trong sự kiện này, Resonators sẽ được tăng cường đặc biệt từ Hợp Kim. Hãy tận dụng những tăng cường này và tham gia vào những trận chiến sôi động!</t>
+[Quy Tắc Sự Kiện]
+Trong sự kiện này, Resonator sẽ được tăng cường đặc biệt từ Hợp Kim. Hãy tận dụng những tăng cường này và tham gia vào những trận chiến sôi động!</t>
         </is>
       </c>
     </row>
@@ -28436,7 +28436,7 @@
 Điều kiện tham gia
 Đạt Cấp Liên minh 14.
 Quy tắc sự kiện
-Trong sự kiện này, Resonators sẽ được tăng cường sức mạnh đặc biệt từ các Hợp kim. Hãy tận dụng những tăng cường này và tham gia vào những trận chiến sôi động!</t>
+Trong sự kiện này, Resonator sẽ được tăng cường sức mạnh đặc biệt từ các Hợp kim. Hãy tận dụng những tăng cường này và tham gia vào những trận chiến sôi động!</t>
         </is>
       </c>
     </row>
@@ -28503,9 +28503,9 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>1. Bạn có thể sử dụng Preparation Credits và Quỹ để thực hiện các Nguyện Ước trong &lt;color=#8c7e51&gt;Nguyện Ước Lều Trại&lt;/color&gt;. Mỗi Nguyện Ước sẽ có chi phí tài nguyên riêng.
-2. Hoàn thành Nguyện Ước sẽ giúp bạn kiếm được Quỹ và Wish Tag. Thiết lập kỷ lục mới sẽ tăng Độ Nổi Tiếng.
-3. Hãy cử Companions phù hợp để thực hiện các Nguyện Ước trong &lt;color=#8c7e51&gt;Nguyện Ước Lều Trại&lt;/color&gt;. Bạn có thể xem chi tiết chỉ số của họ trên trang Companions.</t>
+          <t>1. Bạn có thể dùng Tín Dụng Chuẩn Bị và Quỹ để thực hiện các Nguyện Ước trong &lt;color=#8c7e51&gt;Nguyện Ước Lều Trại&lt;/color&gt;. Mỗi Nguyện Ước sẽ có chi phí tài nguyên riêng.
+2. Hoàn thành Nguyện Ước sẽ giúp bạn kiếm được Quỹ và Thẻ Nguyện Ước. Thiết lập kỷ lục mới sẽ tăng Độ Nổi Tiếng.
+3. Hãy cử Đồng Hành phù hợp để thực hiện các Nguyện Ước trong &lt;color=#8c7e51&gt;Nguyện Ước Lều Trại&lt;/color&gt;. Bạn có thể xem chi tiết chỉ số của họ trên trang Đồng Hành.</t>
         </is>
       </c>
     </row>
@@ -28639,7 +28639,7 @@
       <c r="M422" t="inlineStr">
         <is>
           <t>Đang chuẩn bị: Đồng đội của cậu sẽ lần lượt hành động, ghi điểm dựa trên chỉ số của họ.
-Quy tắc tính điểm: Điểm số thay đổi mỗi lượt, vì đồng đội không thể luôn thi đấu ở phong độ đỉnh cao. Tuy nhiên, những Resonator có chỉ số cao hơn sẽ có tiềm năng ghi được điểm số cao hơn.</t>
+Quy tắc tính điểm: Điểm số thay đổi mỗi lượt, vì đồng đội không thể luôn thi đấu ở phong độ đỉnh cao. Tuy nhiên, những Cộng Hưởng Giả có chỉ số cao hơn sẽ có tiềm năng ghi được điểm số cao hơn.</t>
         </is>
       </c>
     </row>
@@ -28706,9 +28706,9 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>1. Companions có thể giúp cậu hoàn thành Điều Ước trong &lt;color=#8c7e51&gt;Lodge Wishes&lt;/color&gt;.
+          <t>1. Đồng Hành có thể giúp cậu hoàn thành Điều Ước trong &lt;color=#8c7e51&gt;Lodge Wishes&lt;/color&gt;.
 2. Họ có ba chỉ số: Kiến Thức, Hành Động và Hợp Tác. Chỉ số càng cao và càng phù hợp với chỉ số đề xuất của Điều Ước thì Đánh Giá Điều Ước càng cao.
-3. Xây dựng và nâng cấp &lt;color=#8c7e51&gt;Fair Stalls&lt;/color&gt; cũng như hoàn thành chuỗi nhiệm vụ &lt;color=#8c7e51&gt;Festival Journal&lt;/color&gt; để mở khóa thêm Companions.</t>
+3. Xây dựng và nâng cấp &lt;color=#8c7e51&gt;Fair Stalls&lt;/color&gt; cũng như hoàn thành chuỗi nhiệm vụ &lt;color=#8c7e51&gt;Festival Journal&lt;/color&gt; để mở khóa thêm Đồng Hành.</t>
         </is>
       </c>
     </row>
@@ -28775,9 +28775,9 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>1. Bạn có thể tương tác với Companions để tăng chỉ số và Cấp Độ Gắn Kết của họ.
-2. Mỗi lần tương tác sẽ tốn một lượng Wish Tag nhất định. Chi phí càng cao, hiệu quả tăng cường càng lớn.
-3. Hoàn thành các Nguyện Ước trong &lt;color=#8c7e51&gt;Nguyện Ước Lều Trại&lt;/color&gt; để nhận Wish Tag.</t>
+          <t>1. Bạn có thể tương tác với Đồng Hành để tăng chỉ số và Cấp Độ Gắn Kết của họ.
+2. Mỗi lần tương tác sẽ tốn một lượng Thẻ Nguyện Ước nhất định. Chi phí càng cao, hiệu quả tăng cường càng lớn.
+3. Hoàn thành các Nguyện Ước trong &lt;color=#8c7e51&gt;Nguyện Ước Lều Trại&lt;/color&gt; để nhận Thẻ Nguyện Ước.</t>
         </is>
       </c>
     </row>
@@ -28846,7 +28846,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>1. Ngư dân đảo Riccioli tuân theo truyền thống làm việc từ bình minh đến hoàng hôn, tin rằng màn đêm thuộc về Cetus the Tidebreaker, người dẫn dắt linh hồn lạc lối trở về.</t>
+          <t>1. Ngư dân đảo Riccioli tuân theo truyền thống làm việc từ bình minh đến hoàng hôn, tin rằng màn đêm thuộc về Cetus Kẻ Phá Thủy Triều, người dẫn dắt linh hồn lạc lối trở về.</t>
         </is>
       </c>
     </row>
@@ -28911,7 +28911,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Đã mở khóa &lt;color=#ffd12f&gt;Cẩm Nang&lt;/color&gt;. Giữ &lt;color=#ffd12f&gt;phím&lt;/color&gt; {0} để mở bảng Cẩm Nang qua bánh xe lệnh và xem &lt;color=#ffd12f&gt;Huấn Luyện Combat&lt;/color&gt;.</t>
+          <t>Đã mở khóa &lt;color=#ffd12f&gt;Cẩm Nang&lt;/color&gt;. Giữ &lt;color=#ffd12f&gt;phím&lt;/color&gt; {0} để mở bảng Cẩm Nang qua bánh xe lệnh và xem &lt;color=#ffd12f&gt;Huấn Luyện Chiến Đấu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28976,7 +28976,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở menu Nhiệm Vụ qua vòng điều hướng. Hoàn thành &lt;color=#ffd12f&gt;Thăng Cấp Giai Đoạn&lt;/color&gt; để nâng giới hạn &lt;color=#ffd12f&gt;Cấp Liên Minh&lt;/color&gt;</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở menu Nhiệm Vụ qua vòng điều hướng. Hoàn thành &lt;color=#ffd12f&gt;Thăng Cấp Giai Đoạn&lt;/color&gt; để nâng giới hạn &lt;color=#ffd12f&gt;Cấp Độ Liên Minh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29042,8 +29042,8 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonators&lt;/color&gt; qua vòng điều hướng.
-Nhận được &lt;color=#ffd12f&gt;Echo&lt;/color&gt; mới. Hãy trang bị Echo để tăng &lt;color=#ffd12f&gt;Stats Resonators&lt;/color&gt;</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua vòng điều hướng.
+Nhận được &lt;color=#ffd12f&gt;Echo&lt;/color&gt; mới. Hãy trang bị Echo để tăng &lt;color=#ffd12f&gt;Chỉ Số Resonator&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29108,7 +29108,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở Sổ tay trong vòng điều hướng. Bạn có thể nhanh chóng chuyển đến các hoạt động trò chơi qua &lt;color=#ffd12f&gt;Sổ tay&lt;/color&gt;</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở Sổ Hướng Dẫn trong vòng điều hướng. Bạn có thể nhanh chóng chuyển đến các hoạt động trò chơi qua &lt;color=#ffd12f&gt;Sổ Hướng Dẫn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Ngoài Đường Vận Chuyển Từ Tính thông thường, còn có những &lt;color=#ffd12f&gt;Đường Dẫn Dịch Chuyển&lt;/color&gt; đặc biệt. Các Đường Dẫn Dịch Chuyển luôn &lt;color=#ffd12f&gt;xuất hiện theo cặp&lt;/color&gt;. Khi Magnetic Cube đi vào một trong hai Đường Dẫn Dịch Chuyển, nó sẽ &lt;color=#ffd12f&gt;ngay lập tức được dịch chuyển&lt;/color&gt; đến vị trí của Đường Dẫn Dịch Chuyển còn lại.</t>
+          <t>Ngoài Đường Vận Chuyển Từ Tính thông thường, còn có những &lt;color=#ffd12f&gt;Đường Dẫn Dịch Chuyển&lt;/color&gt; đặc biệt. Các Đường Dẫn Dịch Chuyển luôn &lt;color=#ffd12f&gt;xuất hiện theo cặp&lt;/color&gt;. Khi Khối Từ Tính đi vào một trong hai Đường Dẫn Dịch Chuyển, nó sẽ &lt;color=#ffd12f&gt;ngay lập tức được dịch chuyển&lt;/color&gt; đến vị trí của Đường Dẫn Dịch Chuyển còn lại.</t>
         </is>
       </c>
     </row>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Trên thế giới Solaris-3, một số rất ít Tacet Discord có ngoại hình đột biến có thể được tìm thấy ngẫu nhiên. Chúng được gọi là "Huyễn Ảnh" vì sự hiếm có cực độ. Hãy đánh bại chúng để mở khóa các Echo Huyễn Ảnh đặc biệt với &lt;color=#ffd12f&gt;ngoại hình Echo&lt;/color&gt; độc đáo.</t>
+          <t>Trên thế giới Solaris-3, một số rất ít Tacet Discord có ngoại hình đột biến có thể được tìm thấy ngẫu nhiên. Chúng được gọi là "Huyễn Ảnh" vì sự hiếm có cực độ. Hãy đánh bại chúng để mở khóa các Tiếng Vọng Huyễn Ảnh đặc biệt với &lt;color=#ffd12f&gt;ngoại hình Tiếng Vọng&lt;/color&gt; độc đáo.</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đã mở khóa &lt;color=#ffd12f&gt;Events&lt;/color&gt;. Giữ &lt;color=#ffd12f&gt;phím&lt;/color&gt; {0} để mở menu Events qua bánh xe lệnh.
+          <t>Đã mở khóa &lt;color=#ffd12f&gt;Sự Kiện&lt;/color&gt;. Giữ &lt;color=#ffd12f&gt;phím&lt;/color&gt; {0} để mở menu Sự Kiện qua bánh xe lệnh.
 Nhấn {1} để &lt;color=#ffd12f&gt;chuyển đổi&lt;/color&gt; tab bánh xe lệnh.</t>
         </is>
       </c>
@@ -29370,7 +29370,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Giai đoạn 1. Jinhsi không thể di chuyển bình thường khi Thời Gian Bị Ngừng. Trong tình huống này, hãy dùng &lt;color=#ffd12f&gt;Points Move Tinh Tú&lt;/color&gt; do Sentinel Jué tạo ra để di chuyển.</t>
+          <t>Giai đoạn 1. Jinhsi không thể di chuyển bình thường khi Thời Gian Bị Ngừng. Trong tình huống này, hãy dùng &lt;color=#ffd12f&gt;Điểm Di Chuyển Tinh Tú&lt;/color&gt; do Sentinel Jué tạo ra để di chuyển.</t>
         </is>
       </c>
     </row>
@@ -29450,7 +29450,7 @@
 Tem Lollo có thể đổi lấy gói hàng đặc biệt Lollo Helper.
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 14.
-Event Rules
+Quy Tắc Sự Kiện
 Trong thời gian diễn ra sự kiện, mỗi ngày cậu có thể hoàn thành Chiến Dịch Lollo một lần để nhận số lượng Tem Lollo nhất định.
 Mỗi Tem Lollo có thể đổi lấy một gói hàng đặc biệt Lollo Helper.
 Có 3 Kho Hàng cho gói Lollo Helper. Sau khi thu thập đủ tất cả gói hàng trong một Kho, Kho tiếp theo sẽ được mở khóa.
@@ -29526,11 +29526,11 @@
       <c r="M435" t="inlineStr">
         <is>
           <t>[Quy Định Sự Kiện]
-Pioneer Association đã chọn Núi Firmament làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Núi Firmament.
-Hoàn thành Survey Tasks và tích lũy Points Khảo Sát để nhận những phần thưởng giá trị từ Pioneer Association.
+Hiệp Hội Tiên Phong đã chọn Núi Firmament làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Núi Firmament.
+Hoàn thành Nhiệm Vụ Khảo Sát và tích lũy Điểm Khảo Sát để nhận những phần thưởng giá trị từ Hiệp Hội Tiên Phong.
 [Đặt Lại Nhiệm Vụ]
-Survey Tasks sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Points Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
-Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nhiệm Vụ Khảo Sát sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Điểm Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
+Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -29610,7 +29610,7 @@
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14 và đến Núi Firmament trong nhiệm vụ chính "Voyage to Firmament."
 Quy tắc sự kiện
-Event gồm bốn giai đoạn, mỗi giai đoạn sẽ mở khóa dần khi bạn tiến triển trong nhiệm vụ chính.
+Sự kiện gồm bốn giai đoạn, mỗi giai đoạn sẽ mở khóa dần khi bạn tiến triển trong nhiệm vụ chính.
 Hoàn thành các nhiệm vụ sự kiện để nhận những phần thưởng hấp dẫn.
 Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận phần thưởng qua thư.
 Lưu ý rằng một số nội dung của sự kiện sẽ không khả dụng khi chơi Chế độ Hợp tác. Theo dõi Nhiệm vụ cũng sẽ không khả dụng trong một số cảnh nhất định của trò chơi.</t>
@@ -29754,12 +29754,12 @@
       <c r="M438" t="inlineStr">
         <is>
           <t>[
-Event Rules]
-Pioneer Association đã chọn Desorock Highland làm chủ đề cho số tiếp theo của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt về Desorock Highland.
-Hoàn thành Survey Tasks và tích lũy Points Khảo Sát để nhận những phần thưởng giá trị từ Pioneer Association.
+Quy Tắc Sự Kiện]
+Hiệp Hội Tiên Phong đã chọn Desorock Highland làm chủ đề cho số tiếp theo của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt về Desorock Highland.
+Hoàn thành Nhiệm Vụ Khảo Sát và tích lũy Điểm Khảo Sát để nhận những phần thưởng giá trị từ Hiệp Hội Tiên Phong.
 [Đặt Lại Nhiệm Vụ]
-Survey Tasks sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Points Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
-Nếu còn phần thưởng nào chưa nhận khi sự kiện kết thúc, ngươi có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nhiệm Vụ Khảo Sát sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Điểm Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
+Nếu còn phần thưởng nào chưa nhận khi sự kiện kết thúc, ngươi có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -29830,11 +29830,11 @@
       <c r="M439" t="inlineStr">
         <is>
           <t>[Quy Định Sự Kiện]
-Pioneer Association đã chọn Bãi Biển Đen làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Bãi Biển Đen.
-Hoàn thành Survey Tasks và tích lũy Points Khảo Sát để nhận những phần thưởng giá trị từ Pioneer Association.
+Hiệp Hội Tiên Phong đã chọn Bãi Biển Đen làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Bãi Biển Đen.
+Hoàn thành Nhiệm Vụ Khảo Sát và tích lũy Điểm Khảo Sát để nhận những phần thưởng giá trị từ Hiệp Hội Tiên Phong.
 [Đặt Lại Nhiệm Vụ]
-Survey Tasks sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Points Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
-Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nhiệm Vụ Khảo Sát sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Điểm Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
+Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -29907,10 +29907,10 @@
       <c r="M440" t="inlineStr">
         <is>
           <t>Về Sự Kiện
-Để khuyến khích các Tiên Phong chia sẻ thêm về hành trình khám phá Jinzhou, Lollo Logistics đã hợp tác với Pioneer Association tổ chức chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn lên xe tải chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
+Để khuyến khích các Tiên Phong chia sẻ thêm về hành trình khám phá Jinzhou, Lollo Logistics đã hợp tác với Hiệp Hội Tiên Phong tổ chức chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn lên xe tải chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 14.
-Event Rules
+Quy Tắc Sự Kiện
 - Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành nhiệm vụ sự kiện mỗi ngày để nhận một số lượng Nhật Ký Phiêu Lưu nhất định.
 - Mỗi Nhật Ký Phiêu Lưu có thể đổi lấy một Gói Phiêu Lưu; Gói Phiêu Lưu chứa cơ chế đặc biệt, khi kích hoạt sẽ mở khóa một lượng lớn phần thưởng.
 - Có 3 Kho Hàng cho Gói Phiêu Lưu. Khi bạn nhận đủ tất cả hàng hóa trong một Kho, Kho tiếp theo sẽ được mở khóa.</t>
@@ -30050,7 +30050,7 @@
       <c r="M442" t="inlineStr">
         <is>
           <t>Huy Hiệu Lửa thường xuất hiện theo bộ và được dùng để phong ấn lối vào di tích hoặc các thiết bị khác.
-Mỗi &lt;color=#ffd12f&gt;Huy Hiệu Lửa&lt;/color&gt; tương ứng với một &lt;color=#ffd12f&gt;Flare Stone&lt;/color&gt;. Người chơi có thể dập tắt Huy Hiệu Lửa bằng cách tiếp cận và kích hoạt Flare Stone tương ứng.
+Mỗi &lt;color=#ffd12f&gt;Huy Hiệu Lửa&lt;/color&gt; tương ứng với một &lt;color=#ffd12f&gt;Đá Lửa&lt;/color&gt;. Người chơi có thể dập tắt Huy Hiệu Lửa bằng cách tiếp cận và kích hoạt Đá Lửa tương ứng.
 Sau khi tất cả Huy Hiệu Lửa trong bộ được dập tắt, phong ấn sẽ được giải.</t>
         </is>
       </c>
@@ -30116,7 +30116,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Biến thành Clang Bang, &lt;color=#ffd12f&gt;nhảy lên&lt;/color&gt; rồi thực hiện &lt;color=#ffd12f&gt;Đòn Lao Xuống&lt;/color&gt; để phá vỡ &lt;color=#ffd12f&gt;Mũi Băng&lt;/color&gt;.</t>
+          <t>Biến hình thành Clang Bang, &lt;color=#ffd12f&gt;nhảy lên&lt;/color&gt; rồi thực hiện &lt;color=#ffd12f&gt;Tấn Công Lao Xuống&lt;/color&gt; để phá vỡ &lt;color=#ffd12f&gt;Mũi Băng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt Tactical Hologram: Ski, Dodgem Móc vào &lt;color=#ffd12f&gt;Điểm Móc&lt;/color&gt; phía trước để bắt đầu trượt.
+          <t>Sau khi kích hoạt Tactical Hologram: Ski, ném Móc vào &lt;color=#ffd12f&gt;Điểm Móc&lt;/color&gt; phía trước để bắt đầu trượt.
 Trượt: Kiếm &lt;color=#ffd12f&gt;điểm&lt;/color&gt; trong lúc trượt và về đích trong thời gian quy định. Cố gắng đạt điểm cao hơn để nhận phần thưởng tốt hơn!</t>
         </is>
       </c>
@@ -30249,7 +30249,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Khi trượt tuyết, di chuyển trái phải để đi qua các &lt;color=#ffd12f&gt;Vòng Tăng Tốc&lt;/color&gt; và &lt;color=#ffd12f&gt;Point Ring&lt;/color&gt;.
+          <t>Khi trượt tuyết, di chuyển trái phải để đi qua các &lt;color=#ffd12f&gt;Vòng Tăng Tốc&lt;/color&gt; và &lt;color=#ffd12f&gt;Vòng Điểm&lt;/color&gt;.
 Đi qua Vòng Tăng Tốc sẽ giúp tăng tốc độ trượt tuyết trong thời gian ngắn.</t>
         </is>
       </c>
@@ -30450,8 +30450,8 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Lối vào Offering Site. Một số lối vào vẫn chưa thể tiếp cận do thiếu &lt;color=#ffd12f&gt;Chìa Khóa Sao Băng&lt;/color&gt;.
-Dùng &lt;color=#ffd12f&gt;Bộ Bay Lơ Lửng&lt;/color&gt; đặt Chìa Khóa Sao Băng vào khe ở trung tâm lối vào để mở Offering Site.</t>
+          <t>Lối vào Địa Điểm Cúng Tế. Một số lối vào vẫn chưa thể tiếp cận do thiếu &lt;color=#ffd12f&gt;Chìa Khóa Sao Băng&lt;/color&gt;.
+Dùng &lt;color=#ffd12f&gt;Bộ Bay Lơ Lửng&lt;/color&gt; đặt Chìa Khóa Sao Băng vào khe ở trung tâm lối vào để mở Địa Điểm Cúng Tế.</t>
         </is>
       </c>
     </row>
@@ -30854,12 +30854,12 @@
         <is>
           <t>[
 Điều Kiện Mở Khóa]
-Hoàn thành Câu Chuyện Sau "The Flaming Red from Tomorrow" để mở khóa.
+Hoàn thành Câu Chuyện Sau "Lửa Đỏ Từ Ngày Mai" để mở khóa.
 [
 Giới Thiệu]
-Platya, một Người Mang Hoa Bờ Đen, đã đến Startorch Academy truy tìm tin đồn về một Miko Ma – những lời đồn đại dường như vang vọng huyền thoại về "Quý Cô Miko" từ quê hương xa xôi của cô. Bị cuốn hút, cậu quyết định cùng cô tìm kiếm.
+Platya, một Người Mang Hoa Bờ Đen, đã đến Học viện Startorch truy tìm tin đồn về một Miko Ma – những lời đồn đại dường như vang vọng huyền thoại về "Quý Cô Miko" từ quê hương xa xôi của cô. Bị cuốn hút, cậu quyết định cùng cô tìm kiếm.
 [
-Rules]
+Quy Tắc]
 Cậu sẽ nhận được một nhiệm vụ ngay khi sự kiện bắt đầu. Mỗi ngày sẽ mở khóa một nhiệm vụ mới, tổng cộng trong bảy ngày.</t>
         </is>
       </c>
@@ -31082,7 +31082,7 @@
         <is>
           <t>Trong Đường Đua Thiên Hà Vô Tận, hãy thử thách bản thân với các màn chơi ngày càng khó hơn.
 1. Hoàn thành một màn để mở khóa màn tiếp theo.
-2. Hoàn thành tất cả mục tiêu của màn để ghi lại đội hình và thời gian hoàn thành của bạn trong Ranking.
+2. Hoàn thành tất cả mục tiêu của màn để ghi lại đội hình và thời gian hoàn thành của bạn trong Bảng Xếp Hạng.
 3. Kỷ lục của bạn sẽ được cập nhật khi bạn hoàn thành tất cả mục tiêu ở màn cao hơn hoặc vượt qua thời gian của chính mình ở màn đã hoàn thành.
 4. Kỷ lục của bạn sẽ bị xóa sau 90 ngày không đăng nhập vào trò chơi.</t>
         </is>
@@ -31158,12 +31158,12 @@
       <c r="M458" t="inlineStr">
         <is>
           <t>Giới thiệu
-Arno, đặc vụ của Black Shores, hiện đang tìm kiếm sự hỗ trợ trong việc thu thập Surveillance Dataset về Lament với phần thưởng hậu hĩnh. Những ai quan tâm, hãy đến nói chuyện với anh ta.
+Arno, đặc vụ của Black Shores, hiện đang tìm kiếm sự hỗ trợ trong việc thu thập Bộ Dữ Liệu Giám Sát về Lament với phần thưởng hậu hĩnh. Những ai quan tâm, hãy đến nói chuyện với anh ta.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính Act VII "Thời Khắc Vạn Niên Tan Băng".
+Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính Chương VII "Thời Khắc Vạn Niên Tan Băng".
 Quy tắc sự kiện
 1. Trong sự kiện, bạn cần kích hoạt các thử thách ở nhiều khu vực khác nhau. Bạn có thể tham gia bất kỳ thử thách nào đã mở khóa bao nhiêu lần tùy thích.
-2. Khi thử thách bắt đầu, Surveillance Dataset sẽ xuất hiện. Hãy cố gắng thu thập càng nhiều càng tốt trong thời gian giới hạn. Khi tất cả dữ liệu hiện có được thu thập, dữ liệu mới sẽ xuất hiện. Bạn thu thập càng nhiều, phần thưởng càng hậu hĩnh.
+2. Khi thử thách bắt đầu, Bộ Dữ Liệu Giám Sát sẽ xuất hiện. Hãy cố gắng thu thập càng nhiều càng tốt trong thời gian giới hạn. Khi tất cả dữ liệu hiện có được thu thập, dữ liệu mới sẽ xuất hiện. Bạn thu thập càng nhiều, phần thưởng càng hậu hĩnh.
 3. Có nhiều mô-đun khác nhau trong thử thách. Hãy sử dụng chúng một cách chiến lược để tăng tốc độ thu thập dữ liệu.
 4. Nếu có phần thưởng chưa nhận sau khi sự kiện kết thúc, chúng sẽ tự động gửi đến hộp thư của bạn khi đăng nhập lại trong vòng 30 ngày.</t>
         </is>
@@ -31233,8 +31233,8 @@
       <c r="M459" t="inlineStr">
         <is>
           <t>1. Giao nộp KU-Cass Cartridge để nâng cấp Data Hub.
-2. Đạt cấp độ mới sẽ nhận thưởng cấp và mở khóa một Outlier: Discord mới.
-3. Đánh bại Outlier: Discord lần đầu để nhận phần thưởng hậu hĩnh.</t>
+2. Đạt cấp độ mới sẽ nhận thưởng cấp và mở khóa một Outlier: Tacet Discord.
+3. Defeat Outlier: Tacet Discords for the first time to get rich rewards.</t>
         </is>
       </c>
     </row>
@@ -31315,8 +31315,8 @@
 Hoàn thành nhiệm vụ sự kiện để nhận phần thưởng giá trị.
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 14 và đến Bãi Biển Đen trong nhiệm vụ chính "Đến Bờ Cuối Cùng".
-Event Rules
-Event gồm ba giai đoạn, mở khóa theo tiến trình nhiệm vụ chính.
+Quy Tắc Sự Kiện
+Sự kiện gồm ba giai đoạn, mở khóa theo tiến trình nhiệm vụ chính.
 Hoàn thành nhiệm vụ sự kiện để nhận phần thưởng giá trị.
 Nếu còn phần thưởng chưa nhận khi sự kiện kết thúc, cậu có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua thư.
 Lưu ý: Một số nội dung sự kiện sẽ không khả dụng khi chơi Co-op. Tính năng Theo Dõi Nhiệm Vụ sẽ không hoạt động trong một số cảnh nhất định.</t>
@@ -31391,11 +31391,11 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>[Loại Mail]
-Có hai loại thư: Mail Đánh Dấu và Mail Thông Mailờng.
-Mail Đánh Dấu sẽ được ghim ở đầu hộp thư và không hết hạn. Nó sẽ không bị xóa khi bạn chọn "Delete Read Mails".
-Mail Thông Mailờng có thời hạn và sẽ tự động bị xóa khi hết hạn.
-[Dung Lượng Hộp Mail]
+          <t>[Loại Thư]
+Có hai loại thư: Thư Đánh Dấu và Thư Thông Thường.
+Thư Đánh Dấu sẽ được ghim ở đầu hộp thư và không hết hạn. Nó sẽ không bị xóa khi bạn chọn "Xóa Thư Đã Đọc".
+Thư Thông Thường có thời hạn và sẽ tự động bị xóa khi hết hạn.
+[Dung Lượng Hộp Thư]
 Hộp thư có thể lưu trữ tối đa 99 thư.
 Khi đạt giới hạn, những thư cũ nhất không có tệp đính kèm hoặc đã nhận tệp đính kèm sẽ tự động bị xóa.
 Hãy nhận tệp đính kèm kịp thời để tránh mất mát do hết hạn và bị xóa.</t>
@@ -31549,8 +31549,8 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Outlier: Discord ban đầu không thể tấn công. Bạn cần nâng cấp cấp độ Trung Tâm Data để mở khóa. Hãy giao &lt;color=#ffd12f&gt;Đạn KU-Cass&lt;/color&gt; cho KU-Cass để nâng cấp Trung Tâm Data.
-Tiêu diệt Outlier: Discord lần đầu tiên để nhận phần thưởng hậu hĩnh.</t>
+          <t>Dị Thể: Tacet Discord cannot be attacked initially. You need to upgrade your Data Hub level to unlock it. Deliver &lt;color=#ffd12f&gt;KU-Cass Cartridges&lt;/color&gt; to KU-Cass to upgrade your Data Hub.
+Defeat Outlier: Tacet Discord for the first time to claim rich rewards.</t>
         </is>
       </c>
     </row>
@@ -31886,7 +31886,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Biến thành &lt;color=#ffd12f&gt;Gulpuff&lt;/color&gt; để tham gia thử thách và về đích trong thời gian quy định.
+          <t>Biến hình thành &lt;color=#ffd12f&gt;Gulpuff&lt;/color&gt; để tham gia thử thách và về đích trong thời gian quy định.
 Dùng nút &lt;color=#ffd12f&gt;Đột Kích&lt;/color&gt; để tăng tốc cho Gulpuff. Dùng nút &lt;color=#ffd12f&gt;Nhảy&lt;/color&gt; để nhảy lên.</t>
         </is>
       </c>
@@ -32022,10 +32022,10 @@
       <c r="M470" t="inlineStr">
         <is>
           <t>Về sự kiện
-Hoàn thành các nhiệm vụ Pioneer Project để nhận những phần thưởng tuyệt vời.
+Hoàn thành các nhiệm vụ Dự Án Tiên Phong để nhận những phần thưởng tuyệt vời.
 Quy tắc sự kiện
-Event gồm bốn giai đoạn. Hoàn thành các thử thách để nhận những phần thưởng giá trị.
-Sau khi bản cập nhật chính thức ra mắt, phần thưởng đã nhận trong Pioneer Project sẽ được gửi đến tài khoản của bạn trên máy chủ chính thức trong vòng 14 ngày làm việc.</t>
+Sự kiện gồm bốn giai đoạn. Hoàn thành các thử thách để nhận những phần thưởng giá trị.
+Sau khi bản cập nhật chính thức ra mắt, phần thưởng đã nhận trong Dự Án Tiên Phong sẽ được gửi đến tài khoản của bạn trên máy chủ chính thức trong vòng 14 ngày làm việc.</t>
         </is>
       </c>
     </row>
@@ -32366,9 +32366,9 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Hoàn thành Rift Runner, Nightmare Revisits và nhiệm vụ "When the Night Knocks" để nhận Dream Shard.
-Thu thập đủ số lượng Dream Shard cần thiết để mở khóa phần thưởng cột mốc tương ứng.
-Bạn có thể nhận Dream Shard bất cứ lúc nào bằng cách tham gia sự kiện.</t>
+          <t>Hoàn thành Rift Runner, Nightmare Revisits và nhiệm vụ "When the Night Knocks" để nhận Mảnh Giấc Mơ.
+Thu thập đủ số lượng Mảnh Giấc Mơ cần thiết để mở khóa phần thưởng cột mốc tương ứng.
+Bạn có thể nhận Mảnh Giấc Mơ bất cứ lúc nào bằng cách tham gia sự kiện.</t>
         </is>
       </c>
     </row>
@@ -32433,7 +32433,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Hoàn thành các mục tiêu Limited-Time Reward để nhận những phần thưởng độc quyền, bao gồm Vũ Khí 4-Star Nổi Bật "Somnoire Anchor" và Dự Ảnh Vũ Khí Nổi Bật "Projection: Somnoire Anchor."</t>
+          <t>Hoàn thành các mục tiêu Phần Thưởng Giới Hạn để nhận những phần thưởng độc quyền, bao gồm Vũ Khí 4 Sao Nổi Bật "Somnoire Anchor" và Dự Ảnh Vũ Khí Nổi Bật "Projection: Somnoire Anchor."</t>
         </is>
       </c>
     </row>
@@ -32498,7 +32498,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Trong Tower of Adversity, kỹ năng của cậu sẽ được thử thách. Hoàn thành các mục tiêu thử thách cụ thể để giành lấy Huy Hiệu. Thu thập đủ Huy Hiệu để nhận những phần thưởng hậu hĩnh.</t>
+          <t>Trong Tháp Nghịch Cảnh, kỹ năng của cậu sẽ được thử thách. Hoàn thành các mục tiêu thử thách cụ thể để giành lấy Huy Hiệu. Thu thập đủ Huy Hiệu để nhận những phần thưởng hậu hĩnh.</t>
         </is>
       </c>
     </row>
@@ -32563,7 +32563,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Tower Thử Thách bao gồm bốn Khu Vực: &lt;color=#c19f51&gt;Stable Zone&lt;/color&gt;, &lt;color=#c19f51&gt;Experiment Zone&lt;/color&gt;, &lt;color=#c19f51&gt;Khu Vực Nguy Hiểm&lt;/color&gt; và &lt;color=#c19f51&gt;Overdrive Zone&lt;/color&gt;. Mỗi Khu Vực có từ một đến ba Tòa Tower, mỗi Tower lại có nhiều Tầng, mỗi Tầng là một thử thách riêng biệt. Hoàn thành các thử thách để mở khóa Tower và Khu Vực mới. Vượt qua tất cả thử thách trong một Khu Vực sẽ mở khóa Khu Vực tiếp theo.</t>
+          <t>Tháp Thử Thách bao gồm bốn Khu Vực: &lt;color=#c19f51&gt;Khu Vực Ổn Định&lt;/color&gt;, &lt;color=#c19f51&gt;Khu Vực Thí Nghiệm&lt;/color&gt;, &lt;color=#c19f51&gt;Khu Vực Nguy Hiểm&lt;/color&gt; và &lt;color=#c19f51&gt;Khu Vực Quá Tải&lt;/color&gt;. Mỗi Khu Vực có từ một đến ba Tòa Tháp, mỗi Tháp lại có nhiều Tầng, mỗi Tầng là một thử thách riêng biệt. Hoàn thành các thử thách để mở khóa Tháp và Khu Vực mới. Vượt qua tất cả thử thách trong một Khu Vực sẽ mở khóa Khu Vực tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -32702,11 +32702,11 @@
         <is>
           <t>Về nhiệm vụ
 Người thừa kế gia tộc Fisalia dường như có một yêu cầu.
-Tại Thessaleo Fells, một Terminal bí ẩn đang nhấp nháy ánh sáng đáng ngờ. Liệu nó đang che giấu bí mật nào của quá khứ?
+Tại Thessaleo Fells, một Thiết bị đầu cuối bí ẩn đang nhấp nháy ánh sáng đáng ngờ. Liệu nó đang che giấu bí mật nào của quá khứ?
 Điều kiện tham gia
 Đạt Cấp Liên Minh 27.
 Cửa hàng Thử thách
-Hoàn thành các Thử thách để nhận Astrites và [Đồng Xu Challenges], có thể đổi lấy nhiều phần thưởng đa dạng tại [Cửa hàng Thử thách].
+Hoàn thành các Thử thách để nhận Astrites và [Đồng Xu Thử Thách], có thể đổi lấy nhiều phần thưởng đa dạng tại [Cửa hàng Thử thách].
 [Tactical Hologram: Phantom Pain] là hoạt động thường trực, có thể trải nghiệm bất cứ lúc nào và sẽ tiếp tục cập nhật trong các phiên bản sau. Hãy theo dõi nhé.</t>
         </is>
       </c>
@@ -32839,7 +32839,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Đến gặp Aria Mummer để truy cập tính năng Archive Giai Điệu. Chọn một bản nhạc trong album để phát. Bạn có thể đặt bản nhạc đã chọn làm nhạc nền quanh Aria Mummer bằng cách bật &lt;color=#ffd12f&gt;Set Làm Nhạc Nền&lt;/color&gt;</t>
+          <t>Đến gặp Aria Mummer để truy cập tính năng Lưu Trữ Giai Điệu. Chọn một bản nhạc trong album để phát. Bạn có thể đặt bản nhạc đã chọn làm nhạc nền quanh Aria Mummer bằng cách bật &lt;color=#ffd12f&gt;Đặt Làm Nhạc Nền&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -32906,7 +32906,7 @@
       <c r="M483" t="inlineStr">
         <is>
           <t>Trên khắp Rinascita, cậu có thể bắt gặp những chiếc hộp mong manh vương vãi khắp nơi. Đập vỡ chúng để khám phá kho báu ẩn giấu bên trong.
-Hãy chú ý đến những chiếc hộp mang huy hiệu gia tộc Montelli, vì chúng chứa Monnaies—một loại tiền cổ có thể đổi lấy phần thưởng tại Averardo Bank.</t>
+Hãy chú ý đến những chiếc hộp mang huy hiệu gia tộc Montelli, vì chúng chứa Monnaies—một loại tiền cổ có thể đổi lấy phần thưởng tại Ngân Hàng Averardo.</t>
         </is>
       </c>
     </row>
@@ -32971,7 +32971,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Đánh bại&lt;/color&gt; các &lt;color=#ffd12f&gt;Tacet Discords&lt;/color&gt; gần đó để đảm bảo kích hoạt thành công &lt;color=#ffd12f&gt;Sound Emulator&lt;/color&gt;. Hoàn thành thử thách để nhận thưởng.</t>
+          <t>Hạ gục các &lt;color=#ffd12f&gt;Tacet Discord&lt;/color&gt; gần đó để đảm bảo kích hoạt thành công &lt;color=#ffd12f&gt;Bộ Mô Phỏng Âm Thanh&lt;/color&gt;. Hoàn thành thử thách để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33038,7 @@
       <c r="M485" t="inlineStr">
         <is>
           <t>Sản phẩm của một Sonoro Sphere sụp đổ, xuất hiện khắp nơi trên thế giới. Nó ghi lại những ký ức không bị méo mó của quá khứ.
-Dùng Grapple để móc và tiếp cận nhanh các Sonance Casket ở Ragunna. Những Plushie Echoes ở Garden Đồ Thất Lạc đang thu thập chúng—có lẽ đến thăm sẽ hé lộ thêm điều gì đó.</t>
+Dùng Grapple để móc và tiếp cận nhanh các Sonance Casket ở Ragunna. Những Plushie Echo ở Vườn Đồ Thất Lạc đang thu thập chúng—có lẽ đến thăm sẽ hé lộ thêm điều gì đó.</t>
         </is>
       </c>
     </row>
@@ -33103,7 +33103,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Một ngôi làng Plushie Echoes trong Garden Đã Mất. Dân làng đang thu thập những Quan Tài Sonance khắp Ragunna để mở khóa Quả Cầu Sonoro bên trong bức tranh biến hình.</t>
+          <t>Một ngôi làng Plushie Echoes trong Vườn Đã Mất. Dân làng đang thu thập những Quan Tài Sonance khắp Ragunna để mở khóa Sonoro Sphere bên trong bức tranh biến hình.</t>
         </is>
       </c>
     </row>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Sử dụng Tiện ích: &lt;color=#ffd12f&gt;Bay&lt;/color&gt; để nhảy lên không trung và bắt đầu bay. Bay là Tiện ích chỉ có ở Jinzhou (bao gồm Mt. Firmament), Black Shores và khu vực Rinascita. Chỉ khả dụng khi không trong trạng thái chiến đấu.</t>
+          <t>Sử dụng Tiện Ích: &lt;color=#ffd12f&gt;Bay&lt;/color&gt; để bật lên không trung và bắt đầu bay lượn. Bay là Tiện Ích chỉ có ở Jinzhou (bao gồm Núi Kiền Khôn), Bờ Biển Đen và khu vực Rinascita. Chỉ khả dụng khi không trong trạng thái chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -33368,8 +33368,8 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Khi đến Điểm Nhảy, sử dụng Công cụ sẽ kích hoạt Biến Hình Echo tự động. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} nút Công cụ để biến thành Cuddle Wuddle và nhảy.
-Hướng camera về Điểm Nhảy tiếp theo và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Công cụ để nhảy tiếp.</t>
+          <t>Khi đến Điểm Nhảy, sử dụng Tiện Ích sẽ kích hoạt Biến Hình Echo tự động. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút Tiện Ích để biến thành Cuddle Wuddle và nhảy.
+Hướng camera về Điểm Nhảy tiếp theo và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Tiện Ích để nhảy tiếp.</t>
         </is>
       </c>
     </row>
@@ -33435,8 +33435,8 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Khi đến Điểm Leo, Công cụ sẽ tự động biến thành Biến Hình Echo. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} nút Công cụ để biến thành Cuddle Wuddle và vượt qua thử thách leo trèo.
-Hướng camera về Điểm Leo tiếp theo và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Công cụ để leo lên.</t>
+          <t>Khi đến Điểm Leo, Tiện Ích sẽ tự động biến thành Biến Hình Echo. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút Tiện Ích để biến thành Cuddle Wuddle và vượt qua thử thách leo trèo.
+Hướng camera về Điểm Leo tiếp theo và {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Tiện Ích để leo lên.</t>
         </is>
       </c>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Khi kim chỉ vào vùng màu cam, kích hoạt chế độ Punch Mạnh. Nhanh chóng {Cus:Ipt,Touch=tap PC=press Gamepad=press} các nút trái và phải để tăng tốc độ đập.</t>
+          <t>Khi kim chỉ vào vùng màu cam, kích hoạt chế độ Đấm Mạnh. Nhanh chóng {Cus:Ipt,Touch=tap PC=press Gamepad=press} các nút trái và phải để tăng tốc độ đập.</t>
         </is>
       </c>
     </row>
@@ -33633,7 +33633,7 @@
       <c r="M494" t="inlineStr">
         <is>
           <t>Đám mây ác mộng với ngọn lửa ma quái.
-Hãy quan sát số lượng ngọn lửa và hấp thụ Nightmare Cloud &lt;color=#ffd12f&gt;theo đúng thứ tự&lt;/color&gt;. Hấp thụ sai thứ tự sẽ làm thử thách phải bắt đầu lại.</t>
+Hãy quan sát số lượng ngọn lửa và hấp thụ Đám Mây Ác Mộng &lt;color=#ffd12f&gt;theo đúng thứ tự&lt;/color&gt;. Hấp thụ sai thứ tự sẽ làm thử thách phải bắt đầu lại.</t>
         </is>
       </c>
     </row>
@@ -33699,8 +33699,8 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Nightmare Cloud không ngừng nhân lên.
-Lottie Lost phải dùng &lt;color=#ffd12f&gt;Quyển Sách Hoàn Thành&lt;/color&gt; và &lt;color=#ffd12f&gt;giữ&lt;/color&gt; nút Hấp Thụ Nâng Cao để &lt;color=#ffd12f&gt;hấp thụ&lt;/color&gt; và loại bỏ tất cả Nightmare Cloud cùng lúc.</t>
+          <t>Đám Mây Ác Mộng không ngừng nhân lên.
+Lottie Lost phải dùng &lt;color=#ffd12f&gt;Quyển Sách Hoàn Thành&lt;/color&gt; và &lt;color=#ffd12f&gt;giữ&lt;/color&gt; nút Hấp Thụ Nâng Cao để &lt;color=#ffd12f&gt;hấp thụ&lt;/color&gt; và loại bỏ tất cả Đám Mây Ác Mộng cùng lúc.</t>
         </is>
       </c>
     </row>
@@ -33767,8 +33767,8 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Lottie Lost hấp thụ sức mạnh từ những câu chuyện trong &lt;color=#ffd12f&gt;Cuốn Sách Hoàn Thành&lt;/color&gt;, tăng cường khả năng hấp thu Mây Nightmare.
-Giữ &lt;color=#ffd12f&gt;nút Hấp Thu Nâng Cao&lt;/color&gt; để hút toàn bộ Mây Nightmare trong phạm vi của cô.
+          <t>Lottie Lost hấp thụ sức mạnh từ những câu chuyện trong &lt;color=#ffd12f&gt;Cuốn Sách Hoàn Thành&lt;/color&gt;, tăng cường khả năng hấp thu Mây Ác Mộng.
+Giữ &lt;color=#ffd12f&gt;nút Hấp Thu Nâng Cao&lt;/color&gt; để hút toàn bộ Mây Ác Mộng trong phạm vi của cô.
 Trạng thái Hấp Thu Nâng Cao chỉ kéo dài trong thời gian giới hạn và có thể được làm mới bằng cách đọc lại Cuốn Sách Hoàn Thành.</t>
         </is>
       </c>
@@ -34100,7 +34100,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Phản công đòn tấn công của &lt;color=#ffd12f&gt;Vitreum Dancer&lt;/color&gt; có thể phá vỡ vũ khí của nó, khiến nó chuyển sang trạng thái &lt;color=#ffd12f&gt;Thịnh Nộ&lt;/color&gt; và trở nên mạnh mẽ hơn.</t>
+          <t>Phản công đòn tấn công của &lt;color=#ffd12f&gt;Vũ Công Pha Lê&lt;/color&gt; có thể phá vỡ vũ khí của nó, khiến nó chuyển sang trạng thái &lt;color=#ffd12f&gt;Thịnh Nộ&lt;/color&gt; và trở nên mạnh mẽ hơn.</t>
         </is>
       </c>
     </row>
